--- a/Weekly Report.xlsx
+++ b/Weekly Report.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="253">
   <si>
     <t>week</t>
   </si>
@@ -3140,6 +3140,9 @@
       <c r="V10" s="23" t="s">
         <v>251</v>
       </c>
+      <c r="W10" s="80" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="11" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>

--- a/Weekly Report.xlsx
+++ b/Weekly Report.xlsx
@@ -1495,27 +1495,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1527,101 +1506,32 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="43">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="34">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1976,6 +1886,49 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>420775</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1971899</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10192871" y="914400"/>
+          <a:ext cx="12003175" cy="5620534"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2818,7 +2771,7 @@
       <c r="U4" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="80" t="s">
+      <c r="V4" s="73" t="s">
         <v>248</v>
       </c>
     </row>
@@ -2991,7 +2944,7 @@
       <c r="U7" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="V7" s="80" t="s">
+      <c r="V7" s="73" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3140,7 +3093,7 @@
       <c r="V10" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="W10" s="80" t="s">
+      <c r="W10" s="73" t="s">
         <v>120</v>
       </c>
     </row>
@@ -3582,10 +3535,10 @@
       <c r="U18" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="V18" s="84" t="s">
+      <c r="V18" s="77" t="s">
         <v>140</v>
       </c>
-      <c r="W18" s="84" t="s">
+      <c r="W18" s="77" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3644,7 +3597,7 @@
       <c r="V19" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="W19" s="84" t="s">
+      <c r="W19" s="77" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3663,13 +3616,13 @@
       <c r="T20" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="U20" s="81" t="s">
+      <c r="U20" s="74" t="s">
         <v>246</v>
       </c>
-      <c r="V20" s="81" t="s">
+      <c r="V20" s="74" t="s">
         <v>247</v>
       </c>
-      <c r="W20" s="81" t="s">
+      <c r="W20" s="74" t="s">
         <v>252</v>
       </c>
     </row>
@@ -3843,172 +3796,172 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B19:C19 B5:E6 A10:F11 G6 A7:G9 B3:G4 A12:G12 A13:H16 B48 D48 B49:D50 B51:C51 B53:B54 A17:XFD18 B52:D52 S11:T11 S7:XFD7 E19:XFD19 S3:XFD4 S12:XFD16 W8:XFD11 T5:XFD6">
-    <cfRule type="cellIs" dxfId="42" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="39" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="cellIs" dxfId="41" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="38" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="cellIs" dxfId="40" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="37" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10">
-    <cfRule type="cellIs" dxfId="39" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="36" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11">
-    <cfRule type="cellIs" dxfId="38" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="35" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="cellIs" dxfId="37" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="34" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H9">
-    <cfRule type="cellIs" dxfId="36" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="33" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7">
-    <cfRule type="cellIs" dxfId="35" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="32" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8:K9 I3 I5:I6 M8:P9 L5:R6 I13:K13 L3:R3 M13:R13 I4:R4 I7:R7 R6:R7 I10:R12 I14:R16">
-    <cfRule type="cellIs" dxfId="34" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="27" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="cellIs" dxfId="33" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="30" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="cellIs" dxfId="32" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="29" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="cellIs" dxfId="31" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="28" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:I9">
-    <cfRule type="cellIs" dxfId="30" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="25" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3">
-    <cfRule type="cellIs" dxfId="29" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="23" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3">
-    <cfRule type="cellIs" dxfId="28" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="22" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8:J9">
-    <cfRule type="cellIs" dxfId="27" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8:L9">
-    <cfRule type="cellIs" dxfId="26" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L13">
-    <cfRule type="cellIs" dxfId="25" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19">
-    <cfRule type="cellIs" dxfId="24" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q8:Q9">
-    <cfRule type="cellIs" dxfId="23" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R8:R9">
-    <cfRule type="cellIs" dxfId="22" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:T10">
-    <cfRule type="cellIs" dxfId="21" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S6">
-    <cfRule type="cellIs" dxfId="20" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S8:S9">
-    <cfRule type="cellIs" dxfId="19" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T8">
-    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T9">
-    <cfRule type="cellIs" dxfId="17" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U9">
-    <cfRule type="cellIs" dxfId="16" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U8">
-    <cfRule type="cellIs" dxfId="15" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10">
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U11">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V11">
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V8">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V9">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4018,6 +3971,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -4060,7 +4014,7 @@
       <c r="D3" s="60"/>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="75" t="s">
         <v>189</v>
       </c>
       <c r="C4" s="63" t="s">
@@ -4071,7 +4025,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="76" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="65" t="s">
@@ -4166,10 +4120,10 @@
       <c r="B12" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="75" t="s">
+      <c r="D12" s="80" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4180,8 +4134,8 @@
       <c r="B13" s="68" t="s">
         <v>207</v>
       </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="75"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="80"/>
     </row>
     <row r="14" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -4202,7 +4156,7 @@
       <c r="B15" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="C15" s="73" t="s">
+      <c r="C15" s="78" t="s">
         <v>211</v>
       </c>
       <c r="D15" s="60"/>
@@ -4214,7 +4168,7 @@
       <c r="B16" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="C16" s="76"/>
+      <c r="C16" s="81"/>
       <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4465,7 +4419,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="82" t="s">
         <v>164</v>
       </c>
       <c r="B2" s="52" t="s">
@@ -4474,143 +4428,143 @@
       <c r="C2" s="41"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="78"/>
+      <c r="A3" s="83"/>
       <c r="B3" s="45" t="s">
         <v>166</v>
       </c>
       <c r="C3" s="42"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="78"/>
+      <c r="A4" s="83"/>
       <c r="B4" s="45" t="s">
         <v>167</v>
       </c>
       <c r="C4" s="42"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="78"/>
+      <c r="A5" s="83"/>
       <c r="B5" s="45" t="s">
         <v>175</v>
       </c>
       <c r="C5" s="42"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="78"/>
+      <c r="A6" s="83"/>
       <c r="B6" s="51" t="s">
         <v>170</v>
       </c>
       <c r="C6" s="42"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="78"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="45" t="s">
         <v>236</v>
       </c>
       <c r="C7" s="42"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="78"/>
+      <c r="A8" s="83"/>
       <c r="B8" s="45" t="s">
         <v>237</v>
       </c>
       <c r="C8" s="42"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="78"/>
+      <c r="A9" s="83"/>
       <c r="B9" s="45" t="s">
         <v>244</v>
       </c>
       <c r="C9" s="42"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="78"/>
+      <c r="A10" s="83"/>
       <c r="B10" s="45"/>
       <c r="C10" s="42"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="78"/>
+      <c r="A11" s="83"/>
       <c r="B11" s="45"/>
       <c r="C11" s="42"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="78"/>
+      <c r="A12" s="83"/>
       <c r="B12" s="45"/>
       <c r="C12" s="42"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="78"/>
+      <c r="A13" s="83"/>
       <c r="B13" s="45"/>
       <c r="C13" s="42"/>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="79"/>
+      <c r="A14" s="84"/>
       <c r="B14" s="46"/>
       <c r="C14" s="43"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="77" t="s">
+      <c r="A15" s="82" t="s">
         <v>165</v>
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="41"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="78"/>
+      <c r="A16" s="83"/>
       <c r="B16" s="45"/>
       <c r="C16" s="42"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="78"/>
+      <c r="A17" s="83"/>
       <c r="B17" s="45"/>
       <c r="C17" s="42"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="78"/>
+      <c r="A18" s="83"/>
       <c r="B18" s="45"/>
       <c r="C18" s="42"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="78"/>
+      <c r="A19" s="83"/>
       <c r="B19" s="45"/>
       <c r="C19" s="42"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="78"/>
+      <c r="A20" s="83"/>
       <c r="B20" s="45"/>
       <c r="C20" s="42"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="78"/>
+      <c r="A21" s="83"/>
       <c r="B21" s="45"/>
       <c r="C21" s="42"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="78"/>
+      <c r="A22" s="83"/>
       <c r="B22" s="45"/>
       <c r="C22" s="42"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="78"/>
+      <c r="A23" s="83"/>
       <c r="B23" s="45"/>
       <c r="C23" s="42"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="78"/>
+      <c r="A24" s="83"/>
       <c r="B24" s="45"/>
       <c r="C24" s="42"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="78"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="45"/>
       <c r="C25" s="42"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="78"/>
+      <c r="A26" s="83"/>
       <c r="B26" s="45"/>
       <c r="C26" s="42"/>
     </row>
     <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="79"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="46"/>
       <c r="C27" s="43"/>
     </row>

--- a/Weekly Report.xlsx
+++ b/Weekly Report.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="254">
   <si>
     <t>week</t>
   </si>
@@ -807,19 +807,30 @@
   <si>
     <t>Page 23, exercises B &amp; C.
 writing exercise from page 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1341,108 +1352,108 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
@@ -1451,10 +1462,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1465,13 +1476,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1491,21 +1502,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1518,14 +1529,17 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3093,8 +3107,8 @@
       <c r="V10" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="W10" s="73" t="s">
-        <v>120</v>
+      <c r="W10" s="85" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -3151,6 +3165,9 @@
       </c>
       <c r="V11" s="23" t="s">
         <v>245</v>
+      </c>
+      <c r="W11" s="85" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">

--- a/Weekly Report.xlsx
+++ b/Weekly Report.xlsx
@@ -13,7 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="weeklyReport" sheetId="1" r:id="rId1"/>
-    <sheet name="gifts" sheetId="4" r:id="rId2"/>
+    <sheet name="gifts" sheetId="4" state="hidden" r:id="rId2"/>
     <sheet name="toDoList" sheetId="3" r:id="rId3"/>
     <sheet name="thingsToLearn" sheetId="2" r:id="rId4"/>
   </sheets>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="264">
   <si>
     <t>week</t>
   </si>
@@ -247,30 +247,13 @@
     <t>Mon 10 am</t>
   </si>
   <si>
-    <t>Mon 11 am</t>
-  </si>
-  <si>
-    <t>Tue 7 pm</t>
-  </si>
-  <si>
-    <t>Sat 9 am</t>
-  </si>
-  <si>
     <t>Office hours</t>
   </si>
   <si>
-    <t>Tue 9 pm,
-Wed 8 am,
-Thu 9 pm</t>
-  </si>
-  <si>
     <t>Computer Systems and Industrial Programming</t>
   </si>
   <si>
     <t>Mentorship and personal growth</t>
-  </si>
-  <si>
-    <t>Foundations for Discrete Mathematics and Data Structures &amp; Algorithms</t>
   </si>
   <si>
     <t>Online Courses</t>
@@ -805,18 +788,62 @@
     <t>duolinguo 92</t>
   </si>
   <si>
-    <t>Page 23, exercises B &amp; C.
-writing exercise from page 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      </t>
+    <t>Data Structures &amp; Algorithms</t>
+  </si>
+  <si>
+    <t>Discrete Mathematics</t>
+  </si>
+  <si>
+    <t>Informal Meeting</t>
+  </si>
+  <si>
+    <t>Mon 9pm</t>
+  </si>
+  <si>
+    <t>Tue 6am</t>
+  </si>
+  <si>
+    <t>Wed 8am, 7pm</t>
+  </si>
+  <si>
+    <t>Fri 8 am</t>
+  </si>
+  <si>
+    <t>Sat 7pm</t>
+  </si>
+  <si>
+    <t>Sat 8pm</t>
+  </si>
+  <si>
+    <t>attended class</t>
+  </si>
+  <si>
+    <t>108/200</t>
+  </si>
+  <si>
+    <t>31/3850 (26 java)</t>
+  </si>
+  <si>
+    <t>duolinguo 93</t>
+  </si>
+  <si>
+    <t>Hyperfocus - 70%</t>
+  </si>
+  <si>
+    <t>Page 23, exercises B &amp; C.writing exercise from page 25</t>
+  </si>
+  <si>
+    <t>Hyperfocus - finished</t>
+  </si>
+  <si>
+    <t>duolinguo 94</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -931,8 +958,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -975,8 +1018,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1348,11 +1403,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1411,9 +1479,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1538,9 +1603,36 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1911,8 +2003,8 @@
     <xdr:to>
       <xdr:col>46</xdr:col>
       <xdr:colOff>420775</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1971899</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1434016</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2438,16 +2530,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX54"/>
+  <dimension ref="A1:AX56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="19" width="38.21875" style="1" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="32.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="32.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="19" width="38.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="32.77734375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="32.44140625" style="1" customWidth="1"/>
     <col min="22" max="23" width="29.6640625" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="8.88671875" style="1"/>
+    <col min="24" max="24" width="24" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -2605,74 +2698,74 @@
       <c r="B2" s="17"/>
       <c r="C2" s="15" t="str">
         <f>CONCATENATE(TEXT(45929+(C$1-1)*7,"MMM.DD")," - ",TEXT(45929+(C$1-1)*7+6,"MMM.DD"))</f>
-        <v>Sep.29 - Oct.05</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="D2" s="15" t="str">
         <f t="shared" ref="D2:R2" si="0">CONCATENATE(TEXT(45929+(D$1-1)*7,"MMM.DD")," - ",TEXT(45929+(D$1-1)*7+6,"MMM.DD"))</f>
-        <v>Oct.06 - Oct.12</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="E2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Oct.13 - Oct.19</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="F2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Oct.20 - Oct.26</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="G2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Oct.27 - Nov.02</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="H2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Nov.03 - Nov.09</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="I2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Nov.10 - Nov.16</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="J2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Nov.17 - Nov.23</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="K2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Nov.24 - Nov.30</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="L2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Dec.01 - Dec.07</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="M2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Dec.08 - Dec.14</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="N2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Dec.15 - Dec.21</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="O2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Dec.22 - Dec.28</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="P2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Dec.29 - Jan.04</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="Q2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Jan.05 - Jan.11</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="R2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>Jan.12 - Jan.18</v>
+        <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="S2" s="15" t="str">
         <f>CONCATENATE(TEXT(45929+(S$1-1)*7,"МММ.ДД")," - ",TEXT(45929+(S$1-1)*7+6,"МММ.ДД"))</f>
         <v>янв.19 - янв.25</v>
       </c>
       <c r="T2" s="15" t="str">
-        <f t="shared" ref="T2:W2" si="1">CONCATENATE(TEXT(45929+(T$1-1)*7,"МММ.ДД")," - ",TEXT(45929+(T$1-1)*7+6,"МММ.ДД"))</f>
+        <f t="shared" ref="T2:X2" si="1">CONCATENATE(TEXT(45929+(T$1-1)*7,"МММ.ДД")," - ",TEXT(45929+(T$1-1)*7+6,"МММ.ДД"))</f>
         <v>янв.26 - фев.01</v>
       </c>
       <c r="U2" s="15" t="str">
@@ -2687,15 +2780,19 @@
         <f t="shared" si="1"/>
         <v>фев.16 - фев.22</v>
       </c>
-    </row>
-    <row r="3" spans="1:50" s="24" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="X2" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>фев.23 - мар.01</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="27" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="20" t="s">
@@ -2705,38 +2802,39 @@
         <v>38</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I3" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K3" s="24" t="s">
         <v>31</v>
       </c>
       <c r="L3" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q3" s="35" t="s">
-        <v>138</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="Q3" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="W3" s="90"/>
     </row>
     <row r="4" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>70</v>
+      <c r="A4" s="86" t="s">
+        <v>250</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D4" s="9" t="s">
@@ -2746,57 +2844,60 @@
         <v>38</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G4" s="24" t="s">
         <v>31</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>118</v>
+        <v>112</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>113</v>
       </c>
       <c r="J4" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="K4" s="24" t="s">
-        <v>130</v>
-      </c>
       <c r="L4" s="24" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="M4" s="24"/>
       <c r="N4" s="24"/>
       <c r="O4" s="24"/>
       <c r="P4" s="24"/>
-      <c r="Q4" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="R4" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="S4" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="T4" s="55" t="s">
-        <v>178</v>
+      <c r="Q4" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="R4" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="S4" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="T4" s="54" t="s">
+        <v>173</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="V4" s="73" t="s">
-        <v>248</v>
+        <v>98</v>
+      </c>
+      <c r="V4" s="72" t="s">
+        <v>243</v>
+      </c>
+      <c r="W4" s="91" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
-        <v>71</v>
+      <c r="A5" s="86" t="s">
+        <v>251</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="9" t="s">
@@ -2806,7 +2907,7 @@
         <v>44</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G5" s="24" t="s">
         <v>31</v>
@@ -2818,51 +2919,57 @@
         <v>31</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="L5" s="24" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="M5" s="24"/>
       <c r="N5" s="24"/>
       <c r="O5" s="24"/>
       <c r="P5" s="24"/>
       <c r="Q5" s="24" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="R5" s="24" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="T5" s="55" t="s">
-        <v>179</v>
+        <v>141</v>
+      </c>
+      <c r="T5" s="54" t="s">
+        <v>174</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:50" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="W5" s="91" t="s">
+        <v>98</v>
+      </c>
+      <c r="X5" s="91" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="88" t="s">
+        <v>252</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="29"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G6" s="24" t="s">
         <v>31</v>
@@ -2874,42 +2981,48 @@
         <v>31</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="M6" s="24"/>
       <c r="N6" s="24"/>
       <c r="O6" s="24"/>
       <c r="P6" s="24"/>
       <c r="Q6" s="24" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="R6" s="24" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="S6" s="24" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>103</v>
+        <v>98</v>
+      </c>
+      <c r="W6" s="91" t="s">
+        <v>98</v>
+      </c>
+      <c r="X6" s="91" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="29" t="s">
+      <c r="A7" s="85" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="84" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="9" t="s">
@@ -2919,397 +3032,370 @@
         <v>38</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G7" s="24" t="s">
         <v>31</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I7" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K7" s="24" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="L7" s="24" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="M7" s="24"/>
       <c r="N7" s="24"/>
       <c r="O7" s="24"/>
       <c r="P7" s="24"/>
       <c r="Q7" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="R7" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="R7" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="S7" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="S7" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="T7" s="37" t="s">
-        <v>157</v>
+      <c r="T7" s="36" t="s">
+        <v>152</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="V7" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="V7" s="72" t="s">
         <v>66</v>
       </c>
+      <c r="W7" s="91" t="s">
+        <v>256</v>
+      </c>
+      <c r="X7" s="91" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="8" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="J8" s="23" t="s">
-        <v>126</v>
-      </c>
+      <c r="A8" s="86" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="84" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
       <c r="K8" s="24"/>
-      <c r="L8" s="23" t="s">
-        <v>132</v>
-      </c>
+      <c r="L8" s="24"/>
       <c r="M8" s="24"/>
       <c r="N8" s="24"/>
       <c r="O8" s="24"/>
       <c r="P8" s="24"/>
-      <c r="Q8" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="R8" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="S8" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="T8" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="U8" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="V8" s="23" t="s">
+      <c r="Q8" s="24"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="36"/>
+      <c r="T8" s="36"/>
+      <c r="V8" s="72"/>
+      <c r="W8" s="91" t="s">
+        <v>256</v>
+      </c>
+      <c r="X8" s="91" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="86" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="84" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="9" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="C9" s="29"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
-      <c r="G9" s="20"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="23"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
       <c r="K9" s="24"/>
-      <c r="L9" s="21"/>
+      <c r="L9" s="24"/>
       <c r="M9" s="24"/>
       <c r="N9" s="24"/>
       <c r="O9" s="24"/>
       <c r="P9" s="24"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="55" t="s">
-        <v>120</v>
-      </c>
-      <c r="U9" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="V9" s="23" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="10" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="Q9" s="24"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="V9" s="72"/>
+      <c r="W9" s="91" t="s">
+        <v>256</v>
+      </c>
+      <c r="X9" s="91" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18"/>
       <c r="B10" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="G10" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>103</v>
+      <c r="H10" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="K10" s="24"/>
+      <c r="L10" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="M10" s="24"/>
       <c r="N10" s="24"/>
       <c r="O10" s="24"/>
       <c r="P10" s="24"/>
-      <c r="Q10" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="R10" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="S10" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="T10" s="56" t="s">
-        <v>181</v>
+      <c r="Q10" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="R10" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="S10" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="T10" s="23" t="s">
+        <v>175</v>
       </c>
       <c r="U10" s="23" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="V10" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="W10" s="85" t="s">
-        <v>253</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="W10" s="92" t="s">
+        <v>257</v>
+      </c>
+      <c r="X10" s="91"/>
     </row>
     <row r="11" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>
       <c r="B11" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>103</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
       <c r="K11" s="24"/>
-      <c r="L11" s="24" t="s">
-        <v>134</v>
-      </c>
+      <c r="L11" s="21"/>
       <c r="M11" s="24"/>
       <c r="N11" s="24"/>
       <c r="O11" s="24"/>
       <c r="P11" s="24"/>
-      <c r="Q11" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="R11" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="S11" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="T11" s="37" t="s">
-        <v>158</v>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="54" t="s">
+        <v>115</v>
       </c>
       <c r="U11" s="23" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="V11" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="W11" s="85" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="W11" s="92" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="18"/>
       <c r="B12" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G12" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="22" t="s">
-        <v>113</v>
-      </c>
       <c r="I12" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="K12" s="24"/>
+        <v>98</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>115</v>
+      </c>
       <c r="L12" s="24" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="M12" s="24"/>
       <c r="N12" s="24"/>
       <c r="O12" s="24"/>
       <c r="P12" s="24"/>
       <c r="Q12" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="R12" s="24" t="s">
-        <v>31</v>
+        <v>137</v>
+      </c>
+      <c r="R12" s="35" t="s">
+        <v>148</v>
       </c>
       <c r="S12" s="37" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="T12" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="U12" s="71" t="s">
-        <v>31</v>
-      </c>
-      <c r="V12" s="71" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:50" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+      <c r="U12" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="V12" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="W12" s="92" t="s">
+        <v>259</v>
+      </c>
+      <c r="X12" s="92" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18"/>
       <c r="B13" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>115</v>
+        <v>74</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>111</v>
       </c>
       <c r="I13" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J13" s="24" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="K13" s="24"/>
-      <c r="L13" s="22" t="s">
-        <v>115</v>
+      <c r="L13" s="24" t="s">
+        <v>129</v>
       </c>
       <c r="M13" s="24"/>
       <c r="N13" s="24"/>
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
       <c r="Q13" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="R13" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="S13" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="T13" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="U13" s="71" t="s">
-        <v>31</v>
-      </c>
-      <c r="V13" s="71" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="R13" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="S13" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="T13" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="U13" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="V13" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="W13" s="92" t="s">
+        <v>260</v>
+      </c>
+      <c r="X13" s="92" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18"/>
       <c r="B14" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I14" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K14" s="24"/>
       <c r="L14" s="24" t="s">
@@ -3320,46 +3406,49 @@
       <c r="O14" s="24"/>
       <c r="P14" s="24"/>
       <c r="Q14" s="24" t="s">
-        <v>144</v>
+        <v>31</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="S14" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="T14" s="55" t="s">
-        <v>183</v>
-      </c>
-      <c r="U14" s="71" t="s">
-        <v>31</v>
-      </c>
-      <c r="V14" s="71" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:50" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="S14" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="T14" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="U14" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="V14" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="W14" s="93" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="18"/>
       <c r="B15" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>31</v>
+      <c r="H15" s="22" t="s">
+        <v>110</v>
       </c>
       <c r="I15" s="24" t="s">
         <v>31</v>
@@ -3368,51 +3457,63 @@
         <v>31</v>
       </c>
       <c r="K15" s="24"/>
-      <c r="L15" s="24" t="s">
-        <v>31</v>
+      <c r="L15" s="22" t="s">
+        <v>110</v>
       </c>
       <c r="M15" s="24"/>
       <c r="N15" s="24"/>
       <c r="O15" s="24"/>
       <c r="P15" s="24"/>
       <c r="Q15" s="24" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="S15" s="37" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="16" spans="1:50" s="8" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="33"/>
-      <c r="B16" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>2</v>
+        <v>143</v>
+      </c>
+      <c r="S15" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="T15" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="U15" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="V15" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="W15" s="93" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>31</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="I16" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J16" s="24" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="K16" s="24"/>
       <c r="L16" s="24" t="s">
@@ -3423,396 +3524,523 @@
       <c r="O16" s="24"/>
       <c r="P16" s="24"/>
       <c r="Q16" s="24" t="s">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="S16" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="T16" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="U16" s="71" t="s">
-        <v>31</v>
-      </c>
-      <c r="V16" s="71" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="S16" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="T16" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="U16" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="V16" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="W16" s="93" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="R17" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="S17" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="W17" s="93" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" s="8" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="32"/>
+      <c r="B18" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="S18" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="T18" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="U18" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="V18" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="W18" s="93" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B19" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B18" s="6" t="s">
+      <c r="C19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="W19" s="94" t="s">
+        <v>31</v>
+      </c>
+      <c r="X19" s="95" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B20" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R18" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="S18" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="T18" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="U18" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="V18" s="77" t="s">
-        <v>140</v>
-      </c>
-      <c r="W18" s="77" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B19" s="6" t="s">
+      <c r="C20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R20" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="S20" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="T20" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="U20" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="V20" s="76" t="s">
+        <v>135</v>
+      </c>
+      <c r="W20" s="89" t="s">
+        <v>135</v>
+      </c>
+      <c r="X20" s="95" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B21" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="T19" s="57" t="s">
-        <v>89</v>
-      </c>
-      <c r="U19" s="57" t="s">
-        <v>89</v>
-      </c>
-      <c r="V19" s="57" t="s">
-        <v>89</v>
-      </c>
-      <c r="W19" s="77" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="B20" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="3"/>
-      <c r="F20" s="1" t="s">
+      <c r="F21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T21" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="U21" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="V21" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="W21" s="89" t="s">
+        <v>135</v>
+      </c>
+      <c r="X21" s="95" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="B22" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3"/>
+      <c r="F22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="T20" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="U20" s="74" t="s">
-        <v>246</v>
-      </c>
-      <c r="V20" s="74" t="s">
-        <v>247</v>
-      </c>
-      <c r="W20" s="74" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="T22" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="U22" s="73" t="s">
+        <v>241</v>
+      </c>
+      <c r="V22" s="73" t="s">
+        <v>242</v>
+      </c>
+      <c r="W22" s="87" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W23" s="87"/>
+    </row>
+    <row r="24" spans="1:24" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="72" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" s="4" t="s">
+    <row r="25" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B24" s="4" t="s">
+    <row r="26" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B26" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B25" s="1" t="s">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B26" s="1" t="s">
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B28" s="1" t="s">
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B29" s="1" t="s">
+      <c r="E30" s="5"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B31" s="1" t="s">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B32" s="1" t="s">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="2:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B48" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D48" s="24"/>
-    </row>
-    <row r="49" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B49" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-    </row>
-    <row r="50" spans="2:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="B50" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="C50" s="24"/>
+    <row r="50" spans="2:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B50" s="24" t="s">
+        <v>93</v>
+      </c>
       <c r="D50" s="24"/>
     </row>
-    <row r="51" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B51" s="24" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C51" s="24"/>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B52" s="24"/>
+      <c r="D51" s="24"/>
+    </row>
+    <row r="52" spans="2:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="B52" s="35" t="s">
+        <v>144</v>
+      </c>
       <c r="C52" s="24"/>
       <c r="D52" s="24"/>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B54" s="24" t="s">
-        <v>90</v>
+        <v>86</v>
+      </c>
+      <c r="C53" s="24"/>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B55" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B56" s="24" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B19:C19 B5:E6 A10:F11 G6 A7:G9 B3:G4 A12:G12 A13:H16 B48 D48 B49:D50 B51:C51 B53:B54 A17:XFD18 B52:D52 S11:T11 S7:XFD7 E19:XFD19 S3:XFD4 S12:XFD16 W8:XFD11 T5:XFD6">
+  <conditionalFormatting sqref="B21:C21 B5:E6 A12:F13 G6 B3:G4 A14:G14 A15:H18 B50 D50 B51:D52 B53:C53 B55:B56 A19:V20 B54:D54 S13:T13 S7:V9 E21:V21 S3:V4 S14:V18 T5:V6 A10:G11 C7:G9 X3:XFD4 X11:XFD11 Y5:XFD10 X14:XFD21 Y12:XFD13">
     <cfRule type="cellIs" dxfId="33" priority="39" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -3827,12 +4055,12 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G10">
+  <conditionalFormatting sqref="G12">
     <cfRule type="cellIs" dxfId="30" priority="36" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
+  <conditionalFormatting sqref="G13">
     <cfRule type="cellIs" dxfId="29" priority="35" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -3842,17 +4070,17 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H9">
+  <conditionalFormatting sqref="H10:H11">
     <cfRule type="cellIs" dxfId="27" priority="33" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
+  <conditionalFormatting sqref="H7:H9">
     <cfRule type="cellIs" dxfId="26" priority="32" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8:K9 I3 I5:I6 M8:P9 L5:R6 I13:K13 L3:R3 M13:R13 I4:R4 I7:R7 R6:R7 I10:R12 I14:R16">
+  <conditionalFormatting sqref="K10:K11 I3 I5:I6 M10:P11 L5:R6 I15:K15 L3:R3 M15:R15 I4:R4 I7:R9 R6:R9 I12:R14 I16:R18">
     <cfRule type="cellIs" dxfId="25" priority="27" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -3862,7 +4090,7 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
+  <conditionalFormatting sqref="H13">
     <cfRule type="cellIs" dxfId="23" priority="29" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -3872,7 +4100,7 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I8:I9">
+  <conditionalFormatting sqref="I10:I11">
     <cfRule type="cellIs" dxfId="21" priority="25" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -3887,37 +4115,37 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J8:J9">
+  <conditionalFormatting sqref="J10:J11">
     <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L8:L9">
+  <conditionalFormatting sqref="L10:L11">
     <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L13">
+  <conditionalFormatting sqref="L15">
     <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
+  <conditionalFormatting sqref="D21">
     <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q8:Q9">
+  <conditionalFormatting sqref="Q10:Q11">
     <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R8:R9">
+  <conditionalFormatting sqref="R10:R11">
     <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S10:T10">
+  <conditionalFormatting sqref="S12:T12">
     <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -3927,64 +4155,64 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S8:S9">
+  <conditionalFormatting sqref="S10:S11">
     <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T8">
+  <conditionalFormatting sqref="T10">
     <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T9">
+  <conditionalFormatting sqref="T11">
     <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U9">
+  <conditionalFormatting sqref="U11">
     <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U8">
+  <conditionalFormatting sqref="U10">
     <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U10">
+  <conditionalFormatting sqref="U12">
     <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U11">
+  <conditionalFormatting sqref="U13">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V11">
+  <conditionalFormatting sqref="V13">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V10">
+  <conditionalFormatting sqref="V12">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V8">
+  <conditionalFormatting sqref="V10">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V9">
+  <conditionalFormatting sqref="V11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B51" r:id="rId1"/>
-    <hyperlink ref="B48" r:id="rId2"/>
+    <hyperlink ref="B53" r:id="rId1"/>
+    <hyperlink ref="B50" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId3"/>
@@ -3994,7 +4222,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4004,410 +4231,406 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>185</v>
-      </c>
-      <c r="D2" s="60" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="60" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="59"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="74" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="75" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="64" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="D5" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="D3" s="60"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="75" t="s">
-        <v>189</v>
-      </c>
-      <c r="C4" s="63" t="s">
-        <v>185</v>
-      </c>
-      <c r="D4" s="64" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="76" t="s">
-        <v>191</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>192</v>
-      </c>
-      <c r="D5" s="64" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="66" t="s">
-        <v>194</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>195</v>
-      </c>
-      <c r="D6" s="60" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="66" t="s">
-        <v>197</v>
-      </c>
-      <c r="C7" s="59" t="s">
-        <v>198</v>
-      </c>
-      <c r="D7" s="60"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="59"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="58" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" s="59" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="60" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="B9" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="C9" s="62" t="s">
-        <v>190</v>
-      </c>
-      <c r="D9" s="60"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" s="59"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1</v>
       </c>
-      <c r="B10" s="58" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10" s="59" t="s">
-        <v>185</v>
-      </c>
-      <c r="D10" s="60" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1</v>
       </c>
-      <c r="B11" s="61" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="62" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="60"/>
-    </row>
-    <row r="12" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="D11" s="59"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="B12" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="C12" s="78" t="s">
-        <v>190</v>
-      </c>
-      <c r="D12" s="80" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="66" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="77" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12" s="79" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
-      <c r="B13" s="68" t="s">
-        <v>207</v>
-      </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="80"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="67" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="78"/>
+      <c r="D13" s="79"/>
+    </row>
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1</v>
       </c>
-      <c r="B14" s="61" t="s">
-        <v>208</v>
-      </c>
-      <c r="C14" s="62" t="s">
-        <v>209</v>
-      </c>
-      <c r="D14" s="60"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="60" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" s="59"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" s="58" t="s">
-        <v>210</v>
-      </c>
-      <c r="C15" s="78" t="s">
-        <v>211</v>
-      </c>
-      <c r="D15" s="60"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="C15" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="59"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16" s="61" t="s">
-        <v>212</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="60"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="60" t="s">
+        <v>207</v>
+      </c>
+      <c r="C16" s="80"/>
+      <c r="D16" s="59"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1</v>
       </c>
-      <c r="B17" s="66" t="s">
-        <v>213</v>
-      </c>
-      <c r="C17" s="59" t="s">
-        <v>214</v>
-      </c>
-      <c r="D17" s="60"/>
-    </row>
-    <row r="18" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="65" t="s">
+        <v>208</v>
+      </c>
+      <c r="C17" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" s="59"/>
+    </row>
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1</v>
       </c>
-      <c r="B18" s="66" t="s">
-        <v>215</v>
-      </c>
-      <c r="C18" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="D18" s="60"/>
-    </row>
-    <row r="19" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="65" t="s">
+        <v>210</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>211</v>
+      </c>
+      <c r="D18" s="59"/>
+    </row>
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1</v>
       </c>
-      <c r="B19" s="66" t="s">
-        <v>217</v>
-      </c>
-      <c r="C19" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="D19" s="60"/>
-    </row>
-    <row r="20" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="65" t="s">
+        <v>212</v>
+      </c>
+      <c r="C19" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="D19" s="59"/>
+    </row>
+    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1</v>
       </c>
-      <c r="B20" s="66" t="s">
-        <v>219</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="D20" s="60"/>
-    </row>
-    <row r="21" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="D20" s="59"/>
+    </row>
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1</v>
       </c>
-      <c r="B21" s="66" t="s">
-        <v>220</v>
-      </c>
-      <c r="C21" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="D21" s="60"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="C21" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="D21" s="59"/>
+    </row>
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1</v>
       </c>
-      <c r="B22" s="66" t="s">
-        <v>221</v>
-      </c>
-      <c r="C22" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="D22" s="60"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="D22" s="59"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1</v>
       </c>
-      <c r="B23" s="66" t="s">
-        <v>222</v>
-      </c>
-      <c r="C23" s="59" t="s">
+      <c r="B23" s="65" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="D23" s="59"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="D23" s="60"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="69" t="s">
-        <v>223</v>
-      </c>
-      <c r="C24" s="63" t="s">
-        <v>192</v>
-      </c>
-      <c r="D24" s="64" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C24" s="62" t="s">
+        <v>187</v>
+      </c>
+      <c r="D24" s="63" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1</v>
       </c>
-      <c r="B25" s="66" t="s">
-        <v>225</v>
-      </c>
-      <c r="C25" s="59" t="s">
-        <v>192</v>
-      </c>
-      <c r="D25" s="60" t="s">
-        <v>226</v>
+      <c r="B25" s="65" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="59" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="69" t="s">
-        <v>227</v>
-      </c>
-      <c r="C26" s="63" t="s">
-        <v>185</v>
-      </c>
-      <c r="D26" s="64" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="68" t="s">
+        <v>222</v>
+      </c>
+      <c r="C26" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1</v>
       </c>
-      <c r="B27" s="66" t="s">
-        <v>228</v>
-      </c>
-      <c r="C27" s="59" t="s">
-        <v>185</v>
-      </c>
-      <c r="D27" s="60" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="65" t="s">
+        <v>223</v>
+      </c>
+      <c r="C27" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="D27" s="59" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1</v>
       </c>
-      <c r="B28" s="66" t="s">
-        <v>229</v>
-      </c>
-      <c r="C28" s="59" t="s">
-        <v>192</v>
-      </c>
-      <c r="D28" s="60" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="65" t="s">
+        <v>224</v>
+      </c>
+      <c r="C28" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" s="59" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1</v>
       </c>
-      <c r="B29" s="66" t="s">
-        <v>230</v>
-      </c>
-      <c r="C29" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="D29" s="60"/>
-    </row>
-    <row r="30" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="65" t="s">
+        <v>225</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="D29" s="59"/>
+    </row>
+    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1</v>
       </c>
-      <c r="B30" s="66" t="s">
-        <v>231</v>
-      </c>
-      <c r="C30" s="59" t="s">
-        <v>185</v>
-      </c>
-      <c r="D30" s="60" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="65" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="D30" s="59" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1</v>
       </c>
-      <c r="B31" s="66" t="s">
-        <v>233</v>
-      </c>
-      <c r="C31" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="60" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="65" t="s">
+        <v>228</v>
+      </c>
+      <c r="C31" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" s="59" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1</v>
       </c>
-      <c r="B32" s="66" t="s">
-        <v>234</v>
-      </c>
-      <c r="C32" s="59" t="s">
-        <v>192</v>
-      </c>
-      <c r="D32" s="60" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="65" t="s">
+        <v>229</v>
+      </c>
+      <c r="C32" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="59" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1</v>
       </c>
-      <c r="B33" s="66" t="s">
-        <v>235</v>
-      </c>
-      <c r="C33" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="D33" s="70"/>
+      <c r="B33" s="65" t="s">
+        <v>230</v>
+      </c>
+      <c r="C33" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="D33" s="69"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D33">
-    <filterColumn colId="0">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D33"/>
   <mergeCells count="3">
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D13"/>
@@ -4427,190 +4650,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44"/>
-      <c r="B1" s="47" t="s">
+      <c r="A1" s="43"/>
+      <c r="B1" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="40"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="82"/>
+      <c r="B3" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="41"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="82"/>
+      <c r="B4" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="C1" s="48" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="82" t="s">
-        <v>164</v>
-      </c>
-      <c r="B2" s="52" t="s">
-        <v>176</v>
-      </c>
-      <c r="C2" s="41"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="83"/>
-      <c r="B3" s="45" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="42"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="83"/>
-      <c r="B4" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="41"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="83"/>
-      <c r="B5" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="C5" s="42"/>
+      <c r="A5" s="82"/>
+      <c r="B5" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="41"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="83"/>
-      <c r="B6" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="42"/>
+      <c r="A6" s="82"/>
+      <c r="B6" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="41"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="83"/>
-      <c r="B7" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="C7" s="42"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="44" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" s="41"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="83"/>
-      <c r="B8" s="45" t="s">
-        <v>237</v>
-      </c>
-      <c r="C8" s="42"/>
+      <c r="A8" s="82"/>
+      <c r="B8" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="41"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="83"/>
-      <c r="B9" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="C9" s="42"/>
+      <c r="A9" s="82"/>
+      <c r="B9" s="44" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="41"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="83"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="42"/>
+      <c r="A10" s="82"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="41"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="83"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="42"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="41"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="83"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="42"/>
+      <c r="A12" s="82"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="41"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="83"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="42"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="41"/>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="84"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="43"/>
+      <c r="A14" s="83"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="42"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="82" t="s">
-        <v>165</v>
-      </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
+      <c r="A15" s="81" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="83"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="42"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="41"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="83"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="42"/>
+      <c r="A17" s="82"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="41"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="83"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="42"/>
+      <c r="A18" s="82"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="41"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="83"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="42"/>
+      <c r="A19" s="82"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="41"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="83"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="42"/>
+      <c r="A20" s="82"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="41"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="83"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="42"/>
+      <c r="A21" s="82"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="41"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="83"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="42"/>
+      <c r="A22" s="82"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="41"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="83"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="42"/>
+      <c r="A23" s="82"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="41"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="83"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="42"/>
+      <c r="A24" s="82"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="41"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="83"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="42"/>
+      <c r="A25" s="82"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="41"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="83"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="42"/>
+      <c r="A26" s="82"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="41"/>
     </row>
     <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="84"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="43"/>
+      <c r="A27" s="83"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="42"/>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" s="53" t="s">
         <v>169</v>
       </c>
-      <c r="C30" s="54" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B31" s="53" t="s">
-        <v>173</v>
+      <c r="B31" s="52" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="49" t="s">
-        <v>171</v>
+      <c r="B32" s="48" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B33" s="50" t="s">
-        <v>168</v>
+      <c r="B33" s="49" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -4710,12 +4933,12 @@
     </row>
     <row r="132" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E132" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="133" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E133" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Weekly Report.xlsx
+++ b/Weekly Report.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="268">
   <si>
     <t>week</t>
   </si>
@@ -242,9 +242,6 @@
   </si>
   <si>
     <t>Python intensive</t>
-  </si>
-  <si>
-    <t>Mon 10 am</t>
   </si>
   <si>
     <t>Office hours</t>
@@ -803,12 +800,6 @@
     <t>Tue 6am</t>
   </si>
   <si>
-    <t>Wed 8am, 7pm</t>
-  </si>
-  <si>
-    <t>Fri 8 am</t>
-  </si>
-  <si>
     <t>Sat 7pm</t>
   </si>
   <si>
@@ -837,19 +828,57 @@
   </si>
   <si>
     <t>duolinguo 94</t>
+  </si>
+  <si>
+    <t>Sat 9pm</t>
+  </si>
+  <si>
+    <t>Tue 8pm,
+Thu 8pm</t>
+  </si>
+  <si>
+    <t>Wed 8am, 7pm, Fri 8am</t>
+  </si>
+  <si>
+    <t>113/200</t>
+  </si>
+  <si>
+    <t>40/3850 (36 java)</t>
+  </si>
+  <si>
+    <t>33-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1420,105 +1449,105 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
@@ -1527,10 +1556,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1541,13 +1570,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1567,21 +1596,55 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1594,45 +1657,18 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2003,8 +2039,8 @@
     <xdr:to>
       <xdr:col>46</xdr:col>
       <xdr:colOff>420775</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>1434016</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>923028</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2535,12 +2571,25 @@
   <cols>
     <col min="1" max="1" width="10.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="19" width="38.21875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="32.77734375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="32.44140625" style="1" customWidth="1"/>
-    <col min="22" max="23" width="29.6640625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="24" style="1" customWidth="1"/>
-    <col min="25" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="27.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="44.5546875" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="38.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="44.6640625" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="36.6640625" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="42.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="32.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="37.88671875" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="21.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="30.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="16" width="14.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="42.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5546875" style="1" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="37.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="36.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="38.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="23" width="29.6640625" style="1" hidden="1" customWidth="1"/>
+    <col min="24" max="25" width="24.77734375" style="1" customWidth="1"/>
+    <col min="26" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -2701,71 +2750,71 @@
         <v>MMM.DD - MMM.DD</v>
       </c>
       <c r="D2" s="15" t="str">
-        <f t="shared" ref="D2:R2" si="0">CONCATENATE(TEXT(45929+(D$1-1)*7,"MMM.DD")," - ",TEXT(45929+(D$1-1)*7+6,"MMM.DD"))</f>
-        <v>MMM.DD - MMM.DD</v>
+        <f t="shared" ref="D2:R2" si="0">CONCATENATE(TEXT(45929+(D$1-1)*7,"МММ.ДД")," - ",TEXT(45929+(D$1-1)*7+6,"МММ.ДД"))</f>
+        <v>окт.06 - окт.12</v>
       </c>
       <c r="E2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>окт.13 - окт.19</v>
       </c>
       <c r="F2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>окт.20 - окт.26</v>
       </c>
       <c r="G2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>окт.27 - ноя.02</v>
       </c>
       <c r="H2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>ноя.03 - ноя.09</v>
       </c>
       <c r="I2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>ноя.10 - ноя.16</v>
       </c>
       <c r="J2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>ноя.17 - ноя.23</v>
       </c>
       <c r="K2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>ноя.24 - ноя.30</v>
       </c>
       <c r="L2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>дек.01 - дек.07</v>
       </c>
       <c r="M2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>дек.08 - дек.14</v>
       </c>
       <c r="N2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>дек.15 - дек.21</v>
       </c>
       <c r="O2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>дек.22 - дек.28</v>
       </c>
       <c r="P2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>дек.29 - янв.04</v>
       </c>
       <c r="Q2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>янв.05 - янв.11</v>
       </c>
       <c r="R2" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>MMM.DD - MMM.DD</v>
+        <v>янв.12 - янв.18</v>
       </c>
       <c r="S2" s="15" t="str">
         <f>CONCATENATE(TEXT(45929+(S$1-1)*7,"МММ.ДД")," - ",TEXT(45929+(S$1-1)*7+6,"МММ.ДД"))</f>
         <v>янв.19 - янв.25</v>
       </c>
       <c r="T2" s="15" t="str">
-        <f t="shared" ref="T2:X2" si="1">CONCATENATE(TEXT(45929+(T$1-1)*7,"МММ.ДД")," - ",TEXT(45929+(T$1-1)*7+6,"МММ.ДД"))</f>
+        <f t="shared" ref="T2:Y2" si="1">CONCATENATE(TEXT(45929+(T$1-1)*7,"МММ.ДД")," - ",TEXT(45929+(T$1-1)*7+6,"МММ.ДД"))</f>
         <v>янв.26 - фев.01</v>
       </c>
       <c r="U2" s="15" t="str">
@@ -2784,11 +2833,13 @@
         <f t="shared" si="1"/>
         <v>фев.23 - мар.01</v>
       </c>
-    </row>
-    <row r="3" spans="1:50" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="85" t="s">
-        <v>69</v>
-      </c>
+      <c r="Y2" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>мар.02 - мар.08</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" s="24" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="78"/>
       <c r="B3" s="26" t="s">
         <v>68</v>
       </c>
@@ -2802,37 +2853,37 @@
         <v>38</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I3" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K3" s="24" t="s">
         <v>31</v>
       </c>
       <c r="L3" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q3" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="W3" s="90"/>
+        <v>132</v>
+      </c>
+      <c r="W3" s="83"/>
     </row>
     <row r="4" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="86" t="s">
-        <v>250</v>
+      <c r="A4" s="79" t="s">
+        <v>249</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" s="28" t="s">
         <v>31</v>
@@ -2844,58 +2895,61 @@
         <v>38</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G4" s="24" t="s">
         <v>31</v>
       </c>
       <c r="H4" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="I4" s="29" t="s">
-        <v>113</v>
-      </c>
       <c r="J4" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K4" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="L4" s="24" t="s">
         <v>125</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>126</v>
       </c>
       <c r="M4" s="24"/>
       <c r="N4" s="24"/>
       <c r="O4" s="24"/>
       <c r="P4" s="24"/>
       <c r="Q4" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T4" s="54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V4" s="72" t="s">
-        <v>243</v>
-      </c>
-      <c r="W4" s="91" t="s">
-        <v>98</v>
+        <v>242</v>
+      </c>
+      <c r="W4" s="84" t="s">
+        <v>97</v>
+      </c>
+      <c r="X4" s="84" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="86" t="s">
-        <v>251</v>
+      <c r="A5" s="79" t="s">
+        <v>250</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>31</v>
@@ -2907,7 +2961,7 @@
         <v>44</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G5" s="24" t="s">
         <v>31</v>
@@ -2919,57 +2973,60 @@
         <v>31</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L5" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M5" s="24"/>
       <c r="N5" s="24"/>
       <c r="O5" s="24"/>
       <c r="P5" s="24"/>
       <c r="Q5" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R5" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="T5" s="54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="W5" s="91" t="s">
-        <v>98</v>
-      </c>
-      <c r="X5" s="91" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="88" t="s">
-        <v>252</v>
+        <v>97</v>
+      </c>
+      <c r="W5" s="84" t="s">
+        <v>97</v>
+      </c>
+      <c r="X5" s="84" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y5" s="98" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="81" t="s">
+        <v>263</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="28"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G6" s="24" t="s">
         <v>31</v>
@@ -2981,46 +3038,46 @@
         <v>31</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M6" s="24"/>
       <c r="N6" s="24"/>
       <c r="O6" s="24"/>
       <c r="P6" s="24"/>
       <c r="Q6" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R6" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S6" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="W6" s="91" t="s">
-        <v>98</v>
-      </c>
-      <c r="X6" s="91" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="W6" s="84" t="s">
+        <v>97</v>
+      </c>
+      <c r="X6" s="84" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="85" t="s">
-        <v>253</v>
-      </c>
-      <c r="B7" s="84" t="s">
-        <v>248</v>
+      <c r="A7" s="79" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" s="77" t="s">
+        <v>247</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>31</v>
@@ -3032,61 +3089,61 @@
         <v>38</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G7" s="24" t="s">
         <v>31</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I7" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K7" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L7" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M7" s="24"/>
       <c r="N7" s="24"/>
       <c r="O7" s="24"/>
       <c r="P7" s="24"/>
       <c r="Q7" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R7" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="S7" s="36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="T7" s="36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V7" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="W7" s="91" t="s">
-        <v>256</v>
-      </c>
-      <c r="X7" s="91" t="s">
-        <v>256</v>
+      <c r="W7" s="84" t="s">
+        <v>253</v>
+      </c>
+      <c r="X7" s="84" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="86" t="s">
-        <v>254</v>
-      </c>
-      <c r="B8" s="84" t="s">
-        <v>247</v>
+      <c r="A8" s="79" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" s="77" t="s">
+        <v>246</v>
       </c>
       <c r="C8" s="28"/>
       <c r="D8" s="9"/>
@@ -3107,19 +3164,19 @@
       <c r="S8" s="36"/>
       <c r="T8" s="36"/>
       <c r="V8" s="72"/>
-      <c r="W8" s="91" t="s">
-        <v>256</v>
-      </c>
-      <c r="X8" s="91" t="s">
-        <v>256</v>
+      <c r="W8" s="84" t="s">
+        <v>253</v>
+      </c>
+      <c r="X8" s="84" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="86" t="s">
-        <v>255</v>
-      </c>
-      <c r="B9" s="84" t="s">
-        <v>249</v>
+      <c r="A9" s="79" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="77" t="s">
+        <v>248</v>
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="9"/>
@@ -3140,17 +3197,17 @@
       <c r="S9" s="36"/>
       <c r="T9" s="36"/>
       <c r="V9" s="72"/>
-      <c r="W9" s="91" t="s">
-        <v>256</v>
-      </c>
-      <c r="X9" s="91" t="s">
-        <v>256</v>
+      <c r="W9" s="84" t="s">
+        <v>253</v>
+      </c>
+      <c r="X9" s="84" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="10" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18"/>
       <c r="B10" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>31</v>
@@ -3162,55 +3219,57 @@
         <v>42</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K10" s="24"/>
       <c r="L10" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M10" s="24"/>
       <c r="N10" s="24"/>
       <c r="O10" s="24"/>
       <c r="P10" s="24"/>
       <c r="Q10" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R10" s="23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T10" s="23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U10" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="V10" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="W10" s="92" t="s">
-        <v>257</v>
-      </c>
-      <c r="X10" s="91"/>
+        <v>243</v>
+      </c>
+      <c r="W10" s="85" t="s">
+        <v>254</v>
+      </c>
+      <c r="X10" s="85" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="11" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>
       <c r="B11" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="9"/>
@@ -3230,22 +3289,25 @@
       <c r="R11" s="21"/>
       <c r="S11" s="21"/>
       <c r="T11" s="54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="U11" s="23" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="V11" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="W11" s="92" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="12" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+      <c r="W11" s="85" t="s">
+        <v>255</v>
+      </c>
+      <c r="X11" s="85" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18"/>
       <c r="B12" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>31</v>
@@ -3257,59 +3319,59 @@
         <v>67</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G12" s="24" t="s">
         <v>31</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I12" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M12" s="24"/>
       <c r="N12" s="24"/>
       <c r="O12" s="24"/>
       <c r="P12" s="24"/>
       <c r="Q12" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R12" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="S12" s="37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T12" s="55" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="U12" s="23" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="V12" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="W12" s="92" t="s">
-        <v>259</v>
-      </c>
-      <c r="X12" s="92" t="s">
-        <v>263</v>
+        <v>245</v>
+      </c>
+      <c r="W12" s="85" t="s">
+        <v>256</v>
+      </c>
+      <c r="X12" s="85" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18"/>
       <c r="B13" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>31</v>
@@ -3321,57 +3383,57 @@
         <v>39</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G13" s="24" t="s">
         <v>31</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I13" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J13" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K13" s="24"/>
       <c r="L13" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M13" s="24"/>
       <c r="N13" s="24"/>
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
       <c r="Q13" s="24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R13" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S13" s="36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T13" s="36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="U13" s="23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V13" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="W13" s="92" t="s">
-        <v>260</v>
-      </c>
-      <c r="X13" s="92" t="s">
-        <v>262</v>
+        <v>239</v>
+      </c>
+      <c r="W13" s="85" t="s">
+        <v>257</v>
+      </c>
+      <c r="X13" s="85" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18"/>
       <c r="B14" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>31</v>
@@ -3383,19 +3445,19 @@
         <v>31</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I14" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K14" s="24"/>
       <c r="L14" s="24" t="s">
@@ -3423,14 +3485,17 @@
       <c r="V14" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="W14" s="93" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:50" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W14" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="X14" s="86" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18"/>
       <c r="B15" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" s="28" t="s">
         <v>31</v>
@@ -3442,13 +3507,13 @@
         <v>41</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>31</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I15" s="24" t="s">
         <v>31</v>
@@ -3458,23 +3523,23 @@
       </c>
       <c r="K15" s="24"/>
       <c r="L15" s="22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M15" s="24"/>
       <c r="N15" s="24"/>
       <c r="O15" s="24"/>
       <c r="P15" s="24"/>
       <c r="Q15" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="T15" s="54" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="U15" s="70" t="s">
         <v>31</v>
@@ -3482,14 +3547,17 @@
       <c r="V15" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="W15" s="93" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W15" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="X15" s="86" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18"/>
       <c r="B16" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="28" t="s">
         <v>31</v>
@@ -3501,19 +3569,19 @@
         <v>43</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I16" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J16" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K16" s="24"/>
       <c r="L16" s="24" t="s">
@@ -3524,16 +3592,16 @@
       <c r="O16" s="24"/>
       <c r="P16" s="24"/>
       <c r="Q16" s="24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S16" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="T16" s="54" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="U16" s="70" t="s">
         <v>31</v>
@@ -3541,14 +3609,17 @@
       <c r="V16" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="W16" s="93" t="s">
+      <c r="W16" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="X16" s="86" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18"/>
       <c r="B17" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" s="28" t="s">
         <v>31</v>
@@ -3583,22 +3654,25 @@
       <c r="O17" s="24"/>
       <c r="P17" s="24"/>
       <c r="Q17" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R17" s="24" t="s">
         <v>31</v>
       </c>
       <c r="S17" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="W17" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="W17" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="X17" s="86" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:24" s="8" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="32"/>
       <c r="B18" s="33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" s="28" t="s">
         <v>2</v>
@@ -3616,7 +3690,7 @@
         <v>31</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I18" s="24" t="s">
         <v>31</v>
@@ -3650,7 +3724,10 @@
       <c r="V18" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="W18" s="93" t="s">
+      <c r="W18" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="X18" s="86" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3701,13 +3778,13 @@
         <v>31</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="W19" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="X19" s="95" t="s">
-        <v>135</v>
+        <v>134</v>
+      </c>
+      <c r="W19" s="87" t="s">
+        <v>31</v>
+      </c>
+      <c r="X19" s="88" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
@@ -3772,12 +3849,12 @@
         <v>31</v>
       </c>
       <c r="V20" s="76" t="s">
-        <v>135</v>
-      </c>
-      <c r="W20" s="89" t="s">
-        <v>135</v>
-      </c>
-      <c r="X20" s="95" t="s">
+        <v>134</v>
+      </c>
+      <c r="W20" s="82" t="s">
+        <v>134</v>
+      </c>
+      <c r="X20" s="88" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3795,7 +3872,7 @@
         <v>37</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>31</v>
@@ -3819,33 +3896,36 @@
         <v>31</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T21" s="56" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U21" s="56" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V21" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="W21" s="89" t="s">
-        <v>135</v>
-      </c>
-      <c r="X21" s="95" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="W21" s="82" t="s">
+        <v>134</v>
+      </c>
+      <c r="X21" s="88" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="90" t="s">
+        <v>262</v>
+      </c>
       <c r="B22" s="38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="3"/>
@@ -3856,24 +3936,27 @@
         <v>66</v>
       </c>
       <c r="T22" s="39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="U22" s="73" t="s">
+        <v>240</v>
+      </c>
+      <c r="V22" s="73" t="s">
         <v>241</v>
       </c>
-      <c r="V22" s="73" t="s">
-        <v>242</v>
-      </c>
-      <c r="W22" s="87" t="s">
-        <v>261</v>
+      <c r="W22" s="80" t="s">
+        <v>258</v>
+      </c>
+      <c r="X22" s="89" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="W23" s="87"/>
+      <c r="W23" s="80"/>
     </row>
     <row r="24" spans="1:24" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>65</v>
@@ -3881,7 +3964,7 @@
     </row>
     <row r="25" spans="1:24" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>34</v>
@@ -4000,27 +4083,27 @@
     </row>
     <row r="50" spans="2:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B50" s="24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D50" s="24"/>
     </row>
     <row r="51" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B51" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C51" s="24"/>
       <c r="D51" s="24"/>
     </row>
     <row r="52" spans="2:4" ht="72" x14ac:dyDescent="0.3">
       <c r="B52" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C52" s="24"/>
       <c r="D52" s="24"/>
     </row>
     <row r="53" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C53" s="24"/>
     </row>
@@ -4031,16 +4114,16 @@
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B55" s="24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B56" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B21:C21 B5:E6 A12:F13 G6 B3:G4 A14:G14 A15:H18 B50 D50 B51:D52 B53:C53 B55:B56 A19:V20 B54:D54 S13:T13 S7:V9 E21:V21 S3:V4 S14:V18 T5:V6 A10:G11 C7:G9 X3:XFD4 X11:XFD11 Y5:XFD10 X14:XFD21 Y12:XFD13">
+  <conditionalFormatting sqref="B21:C21 B5:E6 A12:F13 G6 B3:G4 A14:G14 A15:H18 B50 D50 B51:D52 B53:C53 B55:B56 A19:V20 B54:D54 S13:T13 S7:V9 E21:V21 S3:V4 S14:V18 T5:V6 A10:G11 C7:G9 X3:XFD3 X19:XFD21 Y4:XFD18">
     <cfRule type="cellIs" dxfId="33" priority="39" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -4236,13 +4319,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="57" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="58" t="s">
         <v>179</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="D2" s="59" t="s">
         <v>180</v>
-      </c>
-      <c r="D2" s="59" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4250,33 +4333,33 @@
         <v>1</v>
       </c>
       <c r="B3" s="60" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="61" t="s">
         <v>182</v>
-      </c>
-      <c r="C3" s="61" t="s">
-        <v>183</v>
       </c>
       <c r="D3" s="59"/>
     </row>
     <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="62" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="63" t="s">
         <v>184</v>
-      </c>
-      <c r="C4" s="62" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="63" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="75" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="D5" s="63" t="s">
         <v>187</v>
-      </c>
-      <c r="D5" s="63" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4284,13 +4367,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="D6" s="59" t="s">
         <v>190</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4298,10 +4381,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="58" t="s">
         <v>192</v>
-      </c>
-      <c r="C7" s="58" t="s">
-        <v>193</v>
       </c>
       <c r="D7" s="59"/>
     </row>
@@ -4310,13 +4393,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="59" t="s">
         <v>194</v>
-      </c>
-      <c r="C8" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="D8" s="59" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4324,10 +4407,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C9" s="61" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D9" s="59"/>
     </row>
@@ -4336,13 +4419,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" s="59" t="s">
         <v>197</v>
-      </c>
-      <c r="C10" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="D10" s="59" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4350,10 +4433,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C11" s="61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" s="59"/>
     </row>
@@ -4362,13 +4445,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="93" t="s">
         <v>200</v>
-      </c>
-      <c r="C12" s="77" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="79" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -4376,20 +4459,20 @@
         <v>1</v>
       </c>
       <c r="B13" s="67" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="78"/>
-      <c r="D13" s="79"/>
+        <v>201</v>
+      </c>
+      <c r="C13" s="92"/>
+      <c r="D13" s="93"/>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="61" t="s">
         <v>203</v>
-      </c>
-      <c r="C14" s="61" t="s">
-        <v>204</v>
       </c>
       <c r="D14" s="59"/>
     </row>
@@ -4398,10 +4481,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="91" t="s">
         <v>205</v>
-      </c>
-      <c r="C15" s="77" t="s">
-        <v>206</v>
       </c>
       <c r="D15" s="59"/>
     </row>
@@ -4410,9 +4493,9 @@
         <v>1</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>207</v>
-      </c>
-      <c r="C16" s="80"/>
+        <v>206</v>
+      </c>
+      <c r="C16" s="94"/>
       <c r="D16" s="59"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4420,10 +4503,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="65" t="s">
+        <v>207</v>
+      </c>
+      <c r="C17" s="58" t="s">
         <v>208</v>
-      </c>
-      <c r="C17" s="58" t="s">
-        <v>209</v>
       </c>
       <c r="D17" s="59"/>
     </row>
@@ -4432,10 +4515,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" s="58" t="s">
         <v>210</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>211</v>
       </c>
       <c r="D18" s="59"/>
     </row>
@@ -4444,10 +4527,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="C19" s="58" t="s">
         <v>212</v>
-      </c>
-      <c r="C19" s="58" t="s">
-        <v>213</v>
       </c>
       <c r="D19" s="59"/>
     </row>
@@ -4456,10 +4539,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D20" s="59"/>
     </row>
@@ -4468,10 +4551,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="65" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D21" s="59"/>
     </row>
@@ -4480,10 +4563,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="65" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D22" s="59"/>
     </row>
@@ -4492,22 +4575,22 @@
         <v>1</v>
       </c>
       <c r="B23" s="65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D23" s="59"/>
     </row>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="68" t="s">
+        <v>217</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>186</v>
+      </c>
+      <c r="D24" s="63" t="s">
         <v>218</v>
-      </c>
-      <c r="C24" s="62" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" s="63" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4515,24 +4598,24 @@
         <v>1</v>
       </c>
       <c r="B25" s="65" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" s="59" t="s">
         <v>220</v>
-      </c>
-      <c r="C25" s="58" t="s">
-        <v>187</v>
-      </c>
-      <c r="D25" s="59" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="68" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C26" s="62" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4540,13 +4623,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="65" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C27" s="58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D27" s="59" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4554,13 +4637,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="65" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C28" s="58" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="59" t="s">
         <v>187</v>
-      </c>
-      <c r="D28" s="59" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4568,10 +4651,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="65" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C29" s="58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D29" s="59"/>
     </row>
@@ -4580,13 +4663,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="65" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="D30" s="59" t="s">
         <v>226</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="D30" s="59" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4594,13 +4677,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="65" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C31" s="58" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D31" s="59" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4608,13 +4691,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="65" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C32" s="58" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D32" s="59" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4622,10 +4705,10 @@
         <v>1</v>
       </c>
       <c r="B33" s="65" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C33" s="58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D33" s="69"/>
     </row>
@@ -4652,188 +4735,188 @@
     <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="43"/>
       <c r="B1" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="C1" s="47" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="95" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="81" t="s">
-        <v>159</v>
-      </c>
       <c r="B2" s="51" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C2" s="40"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="82"/>
+      <c r="A3" s="96"/>
       <c r="B3" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="41"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="96"/>
+      <c r="B4" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="41"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="82"/>
-      <c r="B4" s="44" t="s">
-        <v>162</v>
-      </c>
       <c r="C4" s="41"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="82"/>
+      <c r="A5" s="96"/>
       <c r="B5" s="44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C5" s="41"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="82"/>
+      <c r="A6" s="96"/>
       <c r="B6" s="50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C6" s="41"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="82"/>
+      <c r="A7" s="96"/>
       <c r="B7" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="41"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="96"/>
+      <c r="B8" s="44" t="s">
         <v>231</v>
       </c>
-      <c r="C7" s="41"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="82"/>
-      <c r="B8" s="44" t="s">
-        <v>232</v>
-      </c>
       <c r="C8" s="41"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="82"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C9" s="41"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="82"/>
+      <c r="A10" s="96"/>
       <c r="B10" s="44"/>
       <c r="C10" s="41"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="82"/>
+      <c r="A11" s="96"/>
       <c r="B11" s="44"/>
       <c r="C11" s="41"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="82"/>
+      <c r="A12" s="96"/>
       <c r="B12" s="44"/>
       <c r="C12" s="41"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="82"/>
+      <c r="A13" s="96"/>
       <c r="B13" s="44"/>
       <c r="C13" s="41"/>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="83"/>
+      <c r="A14" s="97"/>
       <c r="B14" s="45"/>
       <c r="C14" s="42"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="81" t="s">
-        <v>160</v>
+      <c r="A15" s="95" t="s">
+        <v>159</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="40"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="82"/>
+      <c r="A16" s="96"/>
       <c r="B16" s="44"/>
       <c r="C16" s="41"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="82"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="44"/>
       <c r="C17" s="41"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="82"/>
+      <c r="A18" s="96"/>
       <c r="B18" s="44"/>
       <c r="C18" s="41"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="82"/>
+      <c r="A19" s="96"/>
       <c r="B19" s="44"/>
       <c r="C19" s="41"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="82"/>
+      <c r="A20" s="96"/>
       <c r="B20" s="44"/>
       <c r="C20" s="41"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="82"/>
+      <c r="A21" s="96"/>
       <c r="B21" s="44"/>
       <c r="C21" s="41"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="82"/>
+      <c r="A22" s="96"/>
       <c r="B22" s="44"/>
       <c r="C22" s="41"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="82"/>
+      <c r="A23" s="96"/>
       <c r="B23" s="44"/>
       <c r="C23" s="41"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="82"/>
+      <c r="A24" s="96"/>
       <c r="B24" s="44"/>
       <c r="C24" s="41"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="82"/>
+      <c r="A25" s="96"/>
       <c r="B25" s="44"/>
       <c r="C25" s="41"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="82"/>
+      <c r="A26" s="96"/>
       <c r="B26" s="44"/>
       <c r="C26" s="41"/>
     </row>
     <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="83"/>
+      <c r="A27" s="97"/>
       <c r="B27" s="45"/>
       <c r="C27" s="42"/>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B30" s="52" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B31" s="52" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="48" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="49" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4933,12 +5016,12 @@
     </row>
     <row r="132" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E132" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="133" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E133" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Weekly Report.xlsx
+++ b/Weekly Report.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="273">
   <si>
     <t>week</t>
   </si>
@@ -850,19 +850,42 @@
   </si>
   <si>
     <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t>finished 3 week tasks</t>
+  </si>
+  <si>
+    <t>120/200</t>
+  </si>
+  <si>
+    <t>56/3887 (48 java)</t>
+  </si>
+  <si>
+    <t>duolinguo 97</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1449,105 +1472,105 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
@@ -1556,10 +1579,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1570,13 +1593,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1596,53 +1619,56 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1657,13 +1683,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2028,49 +2054,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>420775</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>923028</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10192871" y="914400"/>
-          <a:ext cx="12003175" cy="5620534"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2566,7 +2549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX56"/>
+  <dimension ref="A1:AX57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" style="1" bestFit="1" customWidth="1"/>
@@ -2585,11 +2568,14 @@
     <col min="17" max="17" width="42.33203125" style="1" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="19.5546875" style="1" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="37.21875" style="1" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="36.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="36.21875" style="1" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="38.109375" style="1" hidden="1" customWidth="1"/>
     <col min="22" max="23" width="29.6640625" style="1" hidden="1" customWidth="1"/>
-    <col min="24" max="25" width="24.77734375" style="1" customWidth="1"/>
-    <col min="26" max="16384" width="8.88671875" style="1"/>
+    <col min="24" max="25" width="24.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="26" max="27" width="15.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -2814,7 +2800,7 @@
         <v>янв.19 - янв.25</v>
       </c>
       <c r="T2" s="15" t="str">
-        <f t="shared" ref="T2:Y2" si="1">CONCATENATE(TEXT(45929+(T$1-1)*7,"МММ.ДД")," - ",TEXT(45929+(T$1-1)*7+6,"МММ.ДД"))</f>
+        <f t="shared" ref="T2:AD2" si="1">CONCATENATE(TEXT(45929+(T$1-1)*7,"МММ.ДД")," - ",TEXT(45929+(T$1-1)*7+6,"МММ.ДД"))</f>
         <v>янв.26 - фев.01</v>
       </c>
       <c r="U2" s="15" t="str">
@@ -2836,6 +2822,26 @@
       <c r="Y2" s="15" t="str">
         <f t="shared" si="1"/>
         <v>мар.02 - мар.08</v>
+      </c>
+      <c r="Z2" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>мар.09 - мар.15</v>
+      </c>
+      <c r="AA2" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>мар.16 - мар.22</v>
+      </c>
+      <c r="AB2" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>мар.23 - мар.29</v>
+      </c>
+      <c r="AC2" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>мар.30 - апр.05</v>
+      </c>
+      <c r="AD2" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>апр.06 - апр.12</v>
       </c>
     </row>
     <row r="3" spans="1:50" s="24" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
@@ -2943,6 +2949,9 @@
       <c r="X4" s="84" t="s">
         <v>97</v>
       </c>
+      <c r="AB4" s="84" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="5" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="79" t="s">
@@ -3009,8 +3018,11 @@
       <c r="X5" s="84" t="s">
         <v>97</v>
       </c>
-      <c r="Y5" s="98" t="s">
+      <c r="Y5" s="91" t="s">
         <v>267</v>
+      </c>
+      <c r="AB5" s="84" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:50" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -3071,6 +3083,9 @@
       <c r="X6" s="84" t="s">
         <v>97</v>
       </c>
+      <c r="AB6" s="84" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="7" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="79" t="s">
@@ -3135,6 +3150,9 @@
         <v>253</v>
       </c>
       <c r="X7" s="84" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB7" s="84" t="s">
         <v>253</v>
       </c>
     </row>
@@ -3170,6 +3188,9 @@
       <c r="X8" s="84" t="s">
         <v>253</v>
       </c>
+      <c r="AB8" s="84" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="9" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="79" t="s">
@@ -3203,193 +3224,168 @@
       <c r="X9" s="84" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="10" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H10" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="J10" s="23" t="s">
-        <v>120</v>
-      </c>
+      <c r="AB9" s="84" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="79"/>
+      <c r="B10" s="77" t="s">
+        <v>268</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
       <c r="K10" s="24"/>
-      <c r="L10" s="23" t="s">
-        <v>126</v>
-      </c>
+      <c r="L10" s="24"/>
       <c r="M10" s="24"/>
       <c r="N10" s="24"/>
       <c r="O10" s="24"/>
       <c r="P10" s="24"/>
-      <c r="Q10" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="R10" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="S10" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="T10" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="U10" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="V10" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="W10" s="85" t="s">
-        <v>254</v>
-      </c>
-      <c r="X10" s="85" t="s">
-        <v>264</v>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="V10" s="72"/>
+      <c r="W10" s="84"/>
+      <c r="X10" s="84"/>
+      <c r="AB10" s="99" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>
       <c r="B11" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
+        <v>237</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>120</v>
+      </c>
       <c r="K11" s="24"/>
-      <c r="L11" s="21"/>
+      <c r="L11" s="23" t="s">
+        <v>126</v>
+      </c>
       <c r="M11" s="24"/>
       <c r="N11" s="24"/>
       <c r="O11" s="24"/>
       <c r="P11" s="24"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="54" t="s">
-        <v>114</v>
+      <c r="Q11" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="R11" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="S11" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="T11" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="U11" s="23" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="V11" s="23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W11" s="85" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="X11" s="85" t="s">
-        <v>265</v>
+        <v>264</v>
+      </c>
+      <c r="AB11" s="85" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18"/>
       <c r="B12" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="L12" s="24" t="s">
-        <v>97</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="21"/>
       <c r="M12" s="24"/>
       <c r="N12" s="24"/>
       <c r="O12" s="24"/>
       <c r="P12" s="24"/>
-      <c r="Q12" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="R12" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="S12" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="T12" s="55" t="s">
-        <v>175</v>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="54" t="s">
+        <v>114</v>
       </c>
       <c r="U12" s="23" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="V12" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="W12" s="85" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="X12" s="85" t="s">
-        <v>260</v>
+        <v>265</v>
+      </c>
+      <c r="AB12" s="85" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18"/>
       <c r="B13" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>91</v>
+      <c r="D13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="G13" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="31" t="s">
-        <v>110</v>
+      <c r="H13" s="22" t="s">
+        <v>104</v>
       </c>
       <c r="I13" s="24" t="s">
         <v>31</v>
@@ -3397,149 +3393,157 @@
       <c r="J13" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="K13" s="24"/>
+      <c r="K13" s="24" t="s">
+        <v>114</v>
+      </c>
       <c r="L13" s="24" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="M13" s="24"/>
       <c r="N13" s="24"/>
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
       <c r="Q13" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="R13" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="S13" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="T13" s="36" t="s">
-        <v>152</v>
+        <v>136</v>
+      </c>
+      <c r="R13" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="S13" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="T13" s="55" t="s">
+        <v>175</v>
       </c>
       <c r="U13" s="23" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="V13" s="23" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="W13" s="85" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="X13" s="85" t="s">
-        <v>259</v>
+        <v>260</v>
+      </c>
+      <c r="AB13" s="85" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18"/>
       <c r="B14" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>107</v>
+      <c r="D14" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>110</v>
       </c>
       <c r="I14" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="K14" s="24"/>
       <c r="L14" s="24" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="M14" s="24"/>
       <c r="N14" s="24"/>
       <c r="O14" s="24"/>
       <c r="P14" s="24"/>
       <c r="Q14" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="R14" s="24" t="s">
-        <v>31</v>
+        <v>137</v>
+      </c>
+      <c r="R14" s="37" t="s">
+        <v>144</v>
       </c>
       <c r="S14" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="T14" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="U14" s="70" t="s">
-        <v>31</v>
-      </c>
-      <c r="V14" s="70" t="s">
-        <v>31</v>
-      </c>
-      <c r="W14" s="86" t="s">
-        <v>31</v>
-      </c>
-      <c r="X14" s="86" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="T14" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="U14" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="V14" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="W14" s="85" t="s">
+        <v>257</v>
+      </c>
+      <c r="X14" s="85" t="s">
+        <v>259</v>
+      </c>
+      <c r="AB14" s="86" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18"/>
       <c r="B15" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I15" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J15" s="24" t="s">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c r="K15" s="24"/>
-      <c r="L15" s="22" t="s">
-        <v>109</v>
+      <c r="L15" s="24" t="s">
+        <v>31</v>
       </c>
       <c r="M15" s="24"/>
       <c r="N15" s="24"/>
       <c r="O15" s="24"/>
       <c r="P15" s="24"/>
       <c r="Q15" s="24" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
       <c r="T15" s="54" t="s">
-        <v>176</v>
+        <v>31</v>
       </c>
       <c r="U15" s="70" t="s">
         <v>31</v>
@@ -3554,54 +3558,54 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="18"/>
       <c r="B16" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I16" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J16" s="24" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="K16" s="24"/>
-      <c r="L16" s="24" t="s">
-        <v>31</v>
+      <c r="L16" s="22" t="s">
+        <v>109</v>
       </c>
       <c r="M16" s="24"/>
       <c r="N16" s="24"/>
       <c r="O16" s="24"/>
       <c r="P16" s="24"/>
       <c r="Q16" s="24" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="S16" s="36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="T16" s="54" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="U16" s="70" t="s">
         <v>31</v>
@@ -3614,36 +3618,39 @@
       </c>
       <c r="X16" s="86" t="s">
         <v>31</v>
+      </c>
+      <c r="AB16" s="99" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18"/>
       <c r="B17" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="28" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>31</v>
+        <v>98</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>105</v>
       </c>
       <c r="I17" s="24" t="s">
         <v>31</v>
       </c>
       <c r="J17" s="24" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="K17" s="24"/>
       <c r="L17" s="24" t="s">
@@ -3654,13 +3661,22 @@
       <c r="O17" s="24"/>
       <c r="P17" s="24"/>
       <c r="Q17" s="24" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="R17" s="24" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="S17" s="36" t="s">
-        <v>134</v>
+        <v>150</v>
+      </c>
+      <c r="T17" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="U17" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="V17" s="70" t="s">
+        <v>31</v>
       </c>
       <c r="W17" s="86" t="s">
         <v>31</v>
@@ -3669,19 +3685,19 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="8" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="32"/>
-      <c r="B18" s="33" t="s">
-        <v>78</v>
+    <row r="18" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="19" t="s">
+        <v>77</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>31</v>
@@ -3689,8 +3705,8 @@
       <c r="G18" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="22" t="s">
-        <v>108</v>
+      <c r="H18" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="I18" s="24" t="s">
         <v>31</v>
@@ -3707,22 +3723,13 @@
       <c r="O18" s="24"/>
       <c r="P18" s="24"/>
       <c r="Q18" s="24" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="R18" s="24" t="s">
         <v>31</v>
       </c>
       <c r="S18" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="T18" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="U18" s="70" t="s">
-        <v>31</v>
-      </c>
-      <c r="V18" s="70" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="W18" s="86" t="s">
         <v>31</v>
@@ -3731,65 +3738,71 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B19" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="W19" s="87" t="s">
-        <v>31</v>
-      </c>
-      <c r="X19" s="88" t="s">
-        <v>134</v>
+    <row r="19" spans="1:24" s="8" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="32"/>
+      <c r="B19" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="R19" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="S19" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="T19" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="U19" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="V19" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="W19" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="X19" s="86" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>31</v>
@@ -3834,33 +3847,18 @@
         <v>31</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R20" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="S20" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="T20" s="56" t="s">
-        <v>31</v>
-      </c>
-      <c r="U20" s="71" t="s">
-        <v>31</v>
-      </c>
-      <c r="V20" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="W20" s="82" t="s">
+      <c r="W20" s="87" t="s">
+        <v>31</v>
+      </c>
+      <c r="X20" s="88" t="s">
         <v>134</v>
-      </c>
-      <c r="X20" s="88" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>31</v>
@@ -3869,10 +3867,10 @@
         <v>31</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>31</v>
@@ -3892,238 +3890,309 @@
       <c r="L21" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="M21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="P21" s="1" t="s">
         <v>31</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>83</v>
+        <v>31</v>
+      </c>
+      <c r="R21" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="S21" s="38" t="s">
+        <v>31</v>
       </c>
       <c r="T21" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="U21" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="V21" s="56" t="s">
-        <v>83</v>
+        <v>31</v>
+      </c>
+      <c r="U21" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="V21" s="76" t="s">
+        <v>134</v>
       </c>
       <c r="W21" s="82" t="s">
         <v>134</v>
       </c>
       <c r="X21" s="88" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="T22" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="U22" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="V22" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="W22" s="82" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="90" t="s">
+      <c r="X22" s="88" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="90" t="s">
         <v>262</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B23" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="3"/>
-      <c r="F22" s="1" t="s">
+      <c r="C23" s="2"/>
+      <c r="D23" s="3"/>
+      <c r="F23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="T22" s="39" t="s">
+      <c r="T23" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="U22" s="73" t="s">
+      <c r="U23" s="73" t="s">
         <v>240</v>
       </c>
-      <c r="V22" s="73" t="s">
+      <c r="V23" s="73" t="s">
         <v>241</v>
       </c>
-      <c r="W22" s="80" t="s">
+      <c r="W23" s="80" t="s">
         <v>258</v>
       </c>
-      <c r="X22" s="89" t="s">
+      <c r="X23" s="89" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="W23" s="80"/>
-    </row>
-    <row r="24" spans="1:24" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W24" s="80"/>
+    </row>
+    <row r="25" spans="1:24" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="72" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+    <row r="26" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B26" s="4" t="s">
+    <row r="27" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B27" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="E30" s="5"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="2:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B50" s="24" t="s">
+    <row r="51" spans="2:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B51" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="D50" s="24"/>
-    </row>
-    <row r="51" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B51" s="24" t="s">
+      <c r="D51" s="24"/>
+    </row>
+    <row r="52" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B52" s="24" t="s">
         <v>94</v>
-      </c>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-    </row>
-    <row r="52" spans="2:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="B52" s="35" t="s">
-        <v>143</v>
       </c>
       <c r="C52" s="24"/>
       <c r="D52" s="24"/>
     </row>
-    <row r="53" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B53" s="24" t="s">
+    <row r="53" spans="2:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="B53" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+    </row>
+    <row r="54" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B54" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C53" s="24"/>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B54" s="24"/>
       <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B56" s="24" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="56" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B56" s="24" t="s">
+    <row r="57" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B57" s="24" t="s">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B21:C21 B5:E6 A12:F13 G6 B3:G4 A14:G14 A15:H18 B50 D50 B51:D52 B53:C53 B55:B56 A19:V20 B54:D54 S13:T13 S7:V9 E21:V21 S3:V4 S14:V18 T5:V6 A10:G11 C7:G9 X3:XFD3 X19:XFD21 Y4:XFD18">
+  <conditionalFormatting sqref="B22:C22 B5:E6 A13:F14 G6 B3:G4 A15:G15 A16:H19 B51 D51 B52:D53 B54:C54 B56:B57 A20:V21 B55:D55 S14:T14 S7:V10 E22:V22 S3:V4 S15:V19 T5:V6 A11:G12 C7:G10 X3:XFD3 X20:XFD22 Y10:XFD10 Y4:AA9 AC4:XFD9 Y15:XFD19 Y11:AA14 AC11:XFD14">
     <cfRule type="cellIs" dxfId="33" priority="39" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -4138,12 +4207,12 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
+  <conditionalFormatting sqref="G13">
     <cfRule type="cellIs" dxfId="30" priority="36" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
+  <conditionalFormatting sqref="G14">
     <cfRule type="cellIs" dxfId="29" priority="35" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -4153,17 +4222,17 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:H11">
+  <conditionalFormatting sqref="H11:H12">
     <cfRule type="cellIs" dxfId="27" priority="33" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H9">
+  <conditionalFormatting sqref="H7:H10">
     <cfRule type="cellIs" dxfId="26" priority="32" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K10:K11 I3 I5:I6 M10:P11 L5:R6 I15:K15 L3:R3 M15:R15 I4:R4 I7:R9 R6:R9 I12:R14 I16:R18">
+  <conditionalFormatting sqref="K11:K12 I3 I5:I6 M11:P12 L5:R6 I16:K16 L3:R3 M16:R16 I4:R4 I7:R10 R6:R10 I13:R15 I17:R19">
     <cfRule type="cellIs" dxfId="25" priority="27" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -4173,7 +4242,7 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
+  <conditionalFormatting sqref="H14">
     <cfRule type="cellIs" dxfId="23" priority="29" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -4183,7 +4252,7 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10:I11">
+  <conditionalFormatting sqref="I11:I12">
     <cfRule type="cellIs" dxfId="21" priority="25" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -4198,37 +4267,37 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J10:J11">
+  <conditionalFormatting sqref="J11:J12">
     <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L10:L11">
+  <conditionalFormatting sqref="L11:L12">
     <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L15">
+  <conditionalFormatting sqref="L16">
     <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D21">
+  <conditionalFormatting sqref="D22">
     <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q10:Q11">
+  <conditionalFormatting sqref="Q11:Q12">
     <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R10:R11">
+  <conditionalFormatting sqref="R11:R12">
     <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S12:T12">
+  <conditionalFormatting sqref="S13:T13">
     <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
       <formula>"-"</formula>
     </cfRule>
@@ -4238,68 +4307,67 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S10:S11">
+  <conditionalFormatting sqref="S11:S12">
     <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T10">
+  <conditionalFormatting sqref="T11">
     <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T11">
+  <conditionalFormatting sqref="T12">
     <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U11">
+  <conditionalFormatting sqref="U12">
     <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U10">
+  <conditionalFormatting sqref="U11">
     <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U12">
+  <conditionalFormatting sqref="U13">
     <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U13">
+  <conditionalFormatting sqref="U14">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V13">
+  <conditionalFormatting sqref="V14">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V12">
+  <conditionalFormatting sqref="V13">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V10">
+  <conditionalFormatting sqref="V11">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V11">
+  <conditionalFormatting sqref="V12">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B53" r:id="rId1"/>
-    <hyperlink ref="B50" r:id="rId2"/>
+    <hyperlink ref="B54" r:id="rId1"/>
+    <hyperlink ref="B51" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId3"/>
-  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -4447,10 +4515,10 @@
       <c r="B12" s="66" t="s">
         <v>199</v>
       </c>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="92" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="93" t="s">
+      <c r="D12" s="94" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4461,8 +4529,8 @@
       <c r="B13" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="C13" s="92"/>
-      <c r="D13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="94"/>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -4483,7 +4551,7 @@
       <c r="B15" s="57" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="91" t="s">
+      <c r="C15" s="92" t="s">
         <v>205</v>
       </c>
       <c r="D15" s="59"/>
@@ -4495,7 +4563,7 @@
       <c r="B16" s="60" t="s">
         <v>206</v>
       </c>
-      <c r="C16" s="94"/>
+      <c r="C16" s="95"/>
       <c r="D16" s="59"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4742,7 +4810,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="96" t="s">
         <v>158</v>
       </c>
       <c r="B2" s="51" t="s">
@@ -4751,143 +4819,143 @@
       <c r="C2" s="40"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="96"/>
+      <c r="A3" s="97"/>
       <c r="B3" s="44" t="s">
         <v>160</v>
       </c>
       <c r="C3" s="41"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="96"/>
+      <c r="A4" s="97"/>
       <c r="B4" s="44" t="s">
         <v>161</v>
       </c>
       <c r="C4" s="41"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="96"/>
+      <c r="A5" s="97"/>
       <c r="B5" s="44" t="s">
         <v>169</v>
       </c>
       <c r="C5" s="41"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="96"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="50" t="s">
         <v>164</v>
       </c>
       <c r="C6" s="41"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="96"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="44" t="s">
         <v>230</v>
       </c>
       <c r="C7" s="41"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="96"/>
+      <c r="A8" s="97"/>
       <c r="B8" s="44" t="s">
         <v>231</v>
       </c>
       <c r="C8" s="41"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="96"/>
+      <c r="A9" s="97"/>
       <c r="B9" s="44" t="s">
         <v>238</v>
       </c>
       <c r="C9" s="41"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="96"/>
+      <c r="A10" s="97"/>
       <c r="B10" s="44"/>
       <c r="C10" s="41"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="96"/>
+      <c r="A11" s="97"/>
       <c r="B11" s="44"/>
       <c r="C11" s="41"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="96"/>
+      <c r="A12" s="97"/>
       <c r="B12" s="44"/>
       <c r="C12" s="41"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="96"/>
+      <c r="A13" s="97"/>
       <c r="B13" s="44"/>
       <c r="C13" s="41"/>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="97"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="45"/>
       <c r="C14" s="42"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="95" t="s">
+      <c r="A15" s="96" t="s">
         <v>159</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="40"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="96"/>
+      <c r="A16" s="97"/>
       <c r="B16" s="44"/>
       <c r="C16" s="41"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="96"/>
+      <c r="A17" s="97"/>
       <c r="B17" s="44"/>
       <c r="C17" s="41"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="96"/>
+      <c r="A18" s="97"/>
       <c r="B18" s="44"/>
       <c r="C18" s="41"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="96"/>
+      <c r="A19" s="97"/>
       <c r="B19" s="44"/>
       <c r="C19" s="41"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="96"/>
+      <c r="A20" s="97"/>
       <c r="B20" s="44"/>
       <c r="C20" s="41"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="96"/>
+      <c r="A21" s="97"/>
       <c r="B21" s="44"/>
       <c r="C21" s="41"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="96"/>
+      <c r="A22" s="97"/>
       <c r="B22" s="44"/>
       <c r="C22" s="41"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="96"/>
+      <c r="A23" s="97"/>
       <c r="B23" s="44"/>
       <c r="C23" s="41"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="96"/>
+      <c r="A24" s="97"/>
       <c r="B24" s="44"/>
       <c r="C24" s="41"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="96"/>
+      <c r="A25" s="97"/>
       <c r="B25" s="44"/>
       <c r="C25" s="41"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="96"/>
+      <c r="A26" s="97"/>
       <c r="B26" s="44"/>
       <c r="C26" s="41"/>
     </row>
     <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="97"/>
+      <c r="A27" s="98"/>
       <c r="B27" s="45"/>
       <c r="C27" s="42"/>
     </row>

--- a/Weekly Report.xlsx
+++ b/Weekly Report.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="274">
   <si>
     <t>week</t>
   </si>
@@ -865,19 +865,30 @@
   </si>
   <si>
     <t>duolinguo 97</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1472,105 +1483,105 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
@@ -1579,10 +1590,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1593,13 +1604,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1619,53 +1630,56 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1683,13 +1697,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3228,7 +3242,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="10" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="79"/>
       <c r="B10" s="77" t="s">
         <v>268</v>
@@ -3254,7 +3268,7 @@
       <c r="V10" s="72"/>
       <c r="W10" s="84"/>
       <c r="X10" s="84"/>
-      <c r="AB10" s="99" t="s">
+      <c r="AB10" s="92" t="s">
         <v>269</v>
       </c>
     </row>
@@ -3619,11 +3633,11 @@
       <c r="X16" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="AB16" s="99" t="s">
+      <c r="AB16" s="92" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18"/>
       <c r="B17" s="19" t="s">
         <v>76</v>
@@ -3684,8 +3698,11 @@
       <c r="X17" s="86" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AB17" s="100" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="18"/>
       <c r="B18" s="19" t="s">
         <v>77</v>
@@ -3737,8 +3754,11 @@
       <c r="X18" s="86" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" s="8" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AB18" s="100" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" s="8" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="32"/>
       <c r="B19" s="33" t="s">
         <v>78</v>
@@ -3800,7 +3820,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
         <v>36</v>
       </c>
@@ -3856,7 +3876,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>63</v>
       </c>
@@ -3927,7 +3947,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>26</v>
       </c>
@@ -3989,7 +4009,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="90" t="s">
         <v>262</v>
       </c>
@@ -4020,10 +4040,10 @@
         <v>266</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="W24" s="80"/>
     </row>
-    <row r="25" spans="1:24" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>101</v>
       </c>
@@ -4031,7 +4051,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>102</v>
       </c>
@@ -4039,33 +4059,33 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>8</v>
       </c>
@@ -4515,10 +4535,10 @@
       <c r="B12" s="66" t="s">
         <v>199</v>
       </c>
-      <c r="C12" s="92" t="s">
+      <c r="C12" s="93" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="94" t="s">
+      <c r="D12" s="95" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4529,8 +4549,8 @@
       <c r="B13" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="C13" s="93"/>
-      <c r="D13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="95"/>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -4551,7 +4571,7 @@
       <c r="B15" s="57" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="92" t="s">
+      <c r="C15" s="93" t="s">
         <v>205</v>
       </c>
       <c r="D15" s="59"/>
@@ -4563,7 +4583,7 @@
       <c r="B16" s="60" t="s">
         <v>206</v>
       </c>
-      <c r="C16" s="95"/>
+      <c r="C16" s="96"/>
       <c r="D16" s="59"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4810,7 +4830,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="97" t="s">
         <v>158</v>
       </c>
       <c r="B2" s="51" t="s">
@@ -4819,143 +4839,143 @@
       <c r="C2" s="40"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="97"/>
+      <c r="A3" s="98"/>
       <c r="B3" s="44" t="s">
         <v>160</v>
       </c>
       <c r="C3" s="41"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="97"/>
+      <c r="A4" s="98"/>
       <c r="B4" s="44" t="s">
         <v>161</v>
       </c>
       <c r="C4" s="41"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="97"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="44" t="s">
         <v>169</v>
       </c>
       <c r="C5" s="41"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="97"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="50" t="s">
         <v>164</v>
       </c>
       <c r="C6" s="41"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="44" t="s">
         <v>230</v>
       </c>
       <c r="C7" s="41"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="97"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="44" t="s">
         <v>231</v>
       </c>
       <c r="C8" s="41"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="97"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="44" t="s">
         <v>238</v>
       </c>
       <c r="C9" s="41"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="97"/>
+      <c r="A10" s="98"/>
       <c r="B10" s="44"/>
       <c r="C10" s="41"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="97"/>
+      <c r="A11" s="98"/>
       <c r="B11" s="44"/>
       <c r="C11" s="41"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="97"/>
+      <c r="A12" s="98"/>
       <c r="B12" s="44"/>
       <c r="C12" s="41"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="97"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="44"/>
       <c r="C13" s="41"/>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
+      <c r="A14" s="99"/>
       <c r="B14" s="45"/>
       <c r="C14" s="42"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="97" t="s">
         <v>159</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="40"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="97"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="44"/>
       <c r="C16" s="41"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="97"/>
+      <c r="A17" s="98"/>
       <c r="B17" s="44"/>
       <c r="C17" s="41"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="97"/>
+      <c r="A18" s="98"/>
       <c r="B18" s="44"/>
       <c r="C18" s="41"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="97"/>
+      <c r="A19" s="98"/>
       <c r="B19" s="44"/>
       <c r="C19" s="41"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="97"/>
+      <c r="A20" s="98"/>
       <c r="B20" s="44"/>
       <c r="C20" s="41"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="97"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="44"/>
       <c r="C21" s="41"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="97"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="44"/>
       <c r="C22" s="41"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="97"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="44"/>
       <c r="C23" s="41"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="97"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="44"/>
       <c r="C24" s="41"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="97"/>
+      <c r="A25" s="98"/>
       <c r="B25" s="44"/>
       <c r="C25" s="41"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="97"/>
+      <c r="A26" s="98"/>
       <c r="B26" s="44"/>
       <c r="C26" s="41"/>
     </row>
     <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="98"/>
+      <c r="A27" s="99"/>
       <c r="B27" s="45"/>
       <c r="C27" s="42"/>
     </row>

--- a/Weekly Report.xlsx
+++ b/Weekly Report.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="278">
   <si>
     <t>week</t>
   </si>
@@ -868,19 +868,39 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>reviewed videos</t>
+  </si>
+  <si>
+    <t>solve leetcode problems</t>
+  </si>
+  <si>
+    <t>duolinguo 99</t>
+  </si>
+  <si>
+    <t>74/3901 (57 java)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1483,105 +1503,105 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
@@ -1590,10 +1610,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1604,13 +1624,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1630,53 +1650,56 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1697,13 +1720,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1713,7 +1736,27 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2588,8 +2631,10 @@
     <col min="24" max="25" width="24.77734375" style="1" hidden="1" customWidth="1"/>
     <col min="26" max="27" width="15.21875" style="1" hidden="1" customWidth="1"/>
     <col min="28" max="28" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.88671875" style="1"/>
+    <col min="29" max="29" width="15" style="1" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="21.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -2814,7 +2859,7 @@
         <v>янв.19 - янв.25</v>
       </c>
       <c r="T2" s="15" t="str">
-        <f t="shared" ref="T2:AD2" si="1">CONCATENATE(TEXT(45929+(T$1-1)*7,"МММ.ДД")," - ",TEXT(45929+(T$1-1)*7+6,"МММ.ДД"))</f>
+        <f t="shared" ref="T2:AF2" si="1">CONCATENATE(TEXT(45929+(T$1-1)*7,"МММ.ДД")," - ",TEXT(45929+(T$1-1)*7+6,"МММ.ДД"))</f>
         <v>янв.26 - фев.01</v>
       </c>
       <c r="U2" s="15" t="str">
@@ -2857,8 +2902,16 @@
         <f t="shared" si="1"/>
         <v>апр.06 - апр.12</v>
       </c>
-    </row>
-    <row r="3" spans="1:50" s="24" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="AE2" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>апр.13 - апр.19</v>
+      </c>
+      <c r="AF2" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>апр.20 - апр.26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="78"/>
       <c r="B3" s="26" t="s">
         <v>68</v>
@@ -2966,6 +3019,9 @@
       <c r="AB4" s="84" t="s">
         <v>97</v>
       </c>
+      <c r="AD4" s="101" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="5" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="79" t="s">
@@ -3038,6 +3094,9 @@
       <c r="AB5" s="84" t="s">
         <v>97</v>
       </c>
+      <c r="AD5" s="101" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="6" spans="1:50" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="81" t="s">
@@ -3100,6 +3159,9 @@
       <c r="AB6" s="84" t="s">
         <v>253</v>
       </c>
+      <c r="AD6" s="101" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="7" spans="1:50" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="79" t="s">
@@ -3168,6 +3230,9 @@
       </c>
       <c r="AB7" s="84" t="s">
         <v>253</v>
+      </c>
+      <c r="AD7" s="101" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -3205,6 +3270,9 @@
       <c r="AB8" s="84" t="s">
         <v>253</v>
       </c>
+      <c r="AD8" s="101" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="9" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="79" t="s">
@@ -3240,6 +3308,9 @@
       </c>
       <c r="AB9" s="84" t="s">
         <v>253</v>
+      </c>
+      <c r="AD9" s="101" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -3271,6 +3342,9 @@
       <c r="AB10" s="92" t="s">
         <v>269</v>
       </c>
+      <c r="AD10" s="84" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="11" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>
@@ -3377,6 +3451,9 @@
       <c r="AB12" s="85" t="s">
         <v>271</v>
       </c>
+      <c r="AD12" s="85" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="13" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18"/>
@@ -3444,6 +3521,9 @@
       <c r="AB13" s="85" t="s">
         <v>272</v>
       </c>
+      <c r="AD13" s="85" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="14" spans="1:50" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18"/>
@@ -3698,7 +3778,7 @@
       <c r="X17" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="AB17" s="100" t="s">
+      <c r="AB17" s="93" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3754,7 +3834,7 @@
       <c r="X18" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="AB18" s="100" t="s">
+      <c r="AB18" s="93" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4009,7 +4089,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A23" s="90" t="s">
         <v>262</v>
       </c>
@@ -4212,173 +4292,173 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B22:C22 B5:E6 A13:F14 G6 B3:G4 A15:G15 A16:H19 B51 D51 B52:D53 B54:C54 B56:B57 A20:V21 B55:D55 S14:T14 S7:V10 E22:V22 S3:V4 S15:V19 T5:V6 A11:G12 C7:G10 X3:XFD3 X20:XFD22 Y10:XFD10 Y4:AA9 AC4:XFD9 Y15:XFD19 Y11:AA14 AC11:XFD14">
-    <cfRule type="cellIs" dxfId="33" priority="39" operator="equal">
+  <conditionalFormatting sqref="B22:C22 B5:E6 A13:F14 G6 B3:G4 A15:G15 A16:H19 B51 D51 B52:D53 B54:C54 B56:B57 A20:V21 B55:D55 S14:T14 S7:V10 E22:V22 S3:V4 S15:V19 T5:V6 A11:G12 C7:G10 X3:XFD3 X20:XFD22 Y10:AC10 Y4:AA9 Y15:XFD19 Y11:AA14 AC11:XFD11 AC4:XFD9 AE10:XFD10 AC14:XFD14 AC12:AC13 AE12:XFD13">
+    <cfRule type="cellIs" dxfId="35" priority="39" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="cellIs" dxfId="32" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="38" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="cellIs" dxfId="31" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="37" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="cellIs" dxfId="30" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="36" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14">
-    <cfRule type="cellIs" dxfId="29" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="35" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="cellIs" dxfId="28" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="34" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:H12">
-    <cfRule type="cellIs" dxfId="27" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="33" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:H10">
-    <cfRule type="cellIs" dxfId="26" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="32" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K12 I3 I5:I6 M11:P12 L5:R6 I16:K16 L3:R3 M16:R16 I4:R4 I7:R10 R6:R10 I13:R15 I17:R19">
-    <cfRule type="cellIs" dxfId="25" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="27" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="cellIs" dxfId="24" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="30" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="cellIs" dxfId="23" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="29" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="cellIs" dxfId="22" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="28" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11:I12">
-    <cfRule type="cellIs" dxfId="21" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3">
-    <cfRule type="cellIs" dxfId="20" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="23" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3">
-    <cfRule type="cellIs" dxfId="19" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J12">
-    <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L11:L12">
-    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L16">
-    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="18" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22">
-    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q11:Q12">
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R11:R12">
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S13:T13">
-    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S6">
-    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S11:S12">
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T11">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T12">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U12">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U11">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U13">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U14">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V14">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V13">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V11">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V12">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4535,10 +4615,10 @@
       <c r="B12" s="66" t="s">
         <v>199</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="C12" s="94" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="95" t="s">
+      <c r="D12" s="96" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4549,8 +4629,8 @@
       <c r="B13" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="C13" s="94"/>
-      <c r="D13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="96"/>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -4571,7 +4651,7 @@
       <c r="B15" s="57" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="93" t="s">
+      <c r="C15" s="94" t="s">
         <v>205</v>
       </c>
       <c r="D15" s="59"/>
@@ -4583,7 +4663,7 @@
       <c r="B16" s="60" t="s">
         <v>206</v>
       </c>
-      <c r="C16" s="96"/>
+      <c r="C16" s="97"/>
       <c r="D16" s="59"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4830,7 +4910,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="98" t="s">
         <v>158</v>
       </c>
       <c r="B2" s="51" t="s">
@@ -4839,143 +4919,143 @@
       <c r="C2" s="40"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="98"/>
+      <c r="A3" s="99"/>
       <c r="B3" s="44" t="s">
         <v>160</v>
       </c>
       <c r="C3" s="41"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="98"/>
+      <c r="A4" s="99"/>
       <c r="B4" s="44" t="s">
         <v>161</v>
       </c>
       <c r="C4" s="41"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="98"/>
+      <c r="A5" s="99"/>
       <c r="B5" s="44" t="s">
         <v>169</v>
       </c>
       <c r="C5" s="41"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="98"/>
+      <c r="A6" s="99"/>
       <c r="B6" s="50" t="s">
         <v>164</v>
       </c>
       <c r="C6" s="41"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="98"/>
+      <c r="A7" s="99"/>
       <c r="B7" s="44" t="s">
         <v>230</v>
       </c>
       <c r="C7" s="41"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="98"/>
+      <c r="A8" s="99"/>
       <c r="B8" s="44" t="s">
         <v>231</v>
       </c>
       <c r="C8" s="41"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="98"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="44" t="s">
         <v>238</v>
       </c>
       <c r="C9" s="41"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="98"/>
+      <c r="A10" s="99"/>
       <c r="B10" s="44"/>
       <c r="C10" s="41"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="98"/>
+      <c r="A11" s="99"/>
       <c r="B11" s="44"/>
       <c r="C11" s="41"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="98"/>
+      <c r="A12" s="99"/>
       <c r="B12" s="44"/>
       <c r="C12" s="41"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="98"/>
+      <c r="A13" s="99"/>
       <c r="B13" s="44"/>
       <c r="C13" s="41"/>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="99"/>
+      <c r="A14" s="100"/>
       <c r="B14" s="45"/>
       <c r="C14" s="42"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="97" t="s">
+      <c r="A15" s="98" t="s">
         <v>159</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="40"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="98"/>
+      <c r="A16" s="99"/>
       <c r="B16" s="44"/>
       <c r="C16" s="41"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="98"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="44"/>
       <c r="C17" s="41"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="98"/>
+      <c r="A18" s="99"/>
       <c r="B18" s="44"/>
       <c r="C18" s="41"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="98"/>
+      <c r="A19" s="99"/>
       <c r="B19" s="44"/>
       <c r="C19" s="41"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="98"/>
+      <c r="A20" s="99"/>
       <c r="B20" s="44"/>
       <c r="C20" s="41"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="98"/>
+      <c r="A21" s="99"/>
       <c r="B21" s="44"/>
       <c r="C21" s="41"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="98"/>
+      <c r="A22" s="99"/>
       <c r="B22" s="44"/>
       <c r="C22" s="41"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="98"/>
+      <c r="A23" s="99"/>
       <c r="B23" s="44"/>
       <c r="C23" s="41"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="98"/>
+      <c r="A24" s="99"/>
       <c r="B24" s="44"/>
       <c r="C24" s="41"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="98"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="44"/>
       <c r="C25" s="41"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="98"/>
+      <c r="A26" s="99"/>
       <c r="B26" s="44"/>
       <c r="C26" s="41"/>
     </row>
     <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="99"/>
+      <c r="A27" s="100"/>
       <c r="B27" s="45"/>
       <c r="C27" s="42"/>
     </row>
